--- a/data/demog/Guanella/gp_size.xlsx
+++ b/data/demog/Guanella/gp_size.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu-my.sharepoint.com/personal/lipo6619_colorado_edu/Documents/Desktop/Dissertation/natural_demog/data/demog/Guanella/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{9164EAE3-57FE-CB49-A8B6-9E9148CFAEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8223818-4958-A946-B021-EB6758874BD4}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{9164EAE3-57FE-CB49-A8B6-9E9148CFAEEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5A6E523-C95C-E347-9805-8A149C2BA06C}"/>
   <bookViews>
-    <workbookView xWindow="35820" yWindow="-11000" windowWidth="49300" windowHeight="27060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="gp2023demog" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">gp2023demog!$A$1:$S$836</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">gp2023demog!$C$1:$C$836</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">gp2023demog!$A:$S</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">gp2023demog!$1:$1</definedName>
   </definedNames>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="269">
   <si>
     <t>plot</t>
   </si>
@@ -845,6 +845,9 @@
   </si>
   <si>
     <t>not plt D; plt msg '25</t>
+  </si>
+  <si>
+    <t>A2.25</t>
   </si>
 </sst>
 </file>
@@ -1739,7 +1742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1" filterMode="1"/>
   <dimension ref="A1:S836"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="11" customHeight="1"/>
   <cols>
@@ -1805,7 +1808,7 @@
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>15</v>
+        <v>268</v>
       </c>
       <c r="R1" s="2" t="s">
         <v>16</v>
@@ -1814,7 +1817,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="11" customHeight="1">
+    <row r="2" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>18</v>
       </c>
@@ -1873,7 +1876,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="11" customHeight="1">
+    <row r="3" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>18</v>
       </c>
@@ -1930,7 +1933,7 @@
       </c>
       <c r="S3" s="6"/>
     </row>
-    <row r="4" spans="1:19" ht="11" customHeight="1">
+    <row r="4" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>18</v>
       </c>
@@ -1980,7 +1983,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="11" customHeight="1">
+    <row r="5" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>18</v>
       </c>
@@ -2039,7 +2042,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="11" customHeight="1">
+    <row r="6" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>18</v>
       </c>
@@ -2098,7 +2101,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="11" customHeight="1">
+    <row r="7" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
@@ -2155,7 +2158,7 @@
       </c>
       <c r="S7" s="6"/>
     </row>
-    <row r="8" spans="1:19" ht="11" customHeight="1">
+    <row r="8" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>18</v>
       </c>
@@ -2212,7 +2215,7 @@
       </c>
       <c r="S8" s="6"/>
     </row>
-    <row r="9" spans="1:19" ht="11" customHeight="1">
+    <row r="9" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>18</v>
       </c>
@@ -2269,7 +2272,7 @@
       </c>
       <c r="S9" s="6"/>
     </row>
-    <row r="10" spans="1:19" ht="11" customHeight="1">
+    <row r="10" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>18</v>
       </c>
@@ -2326,7 +2329,7 @@
       </c>
       <c r="S10" s="6"/>
     </row>
-    <row r="11" spans="1:19" ht="11" customHeight="1">
+    <row r="11" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>18</v>
       </c>
@@ -2385,7 +2388,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="11" customHeight="1">
+    <row r="12" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -2435,7 +2438,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="11" customHeight="1">
+    <row r="13" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>18</v>
       </c>
@@ -2492,7 +2495,7 @@
       </c>
       <c r="S13" s="6"/>
     </row>
-    <row r="14" spans="1:19" ht="11" customHeight="1">
+    <row r="14" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>18</v>
       </c>
@@ -2549,7 +2552,7 @@
       </c>
       <c r="S14" s="6"/>
     </row>
-    <row r="15" spans="1:19" ht="11" customHeight="1">
+    <row r="15" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
@@ -2606,7 +2609,7 @@
       </c>
       <c r="S15" s="6"/>
     </row>
-    <row r="16" spans="1:19" ht="11" customHeight="1">
+    <row r="16" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>18</v>
       </c>
@@ -2663,7 +2666,7 @@
       </c>
       <c r="S16" s="6"/>
     </row>
-    <row r="17" spans="1:19" ht="11" customHeight="1">
+    <row r="17" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
@@ -2720,7 +2723,7 @@
       </c>
       <c r="S17" s="6"/>
     </row>
-    <row r="18" spans="1:19" ht="11" customHeight="1">
+    <row r="18" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>18</v>
       </c>
@@ -2779,7 +2782,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="11" customHeight="1">
+    <row r="19" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>18</v>
       </c>
@@ -2836,7 +2839,7 @@
       </c>
       <c r="S19" s="6"/>
     </row>
-    <row r="20" spans="1:19" ht="11" customHeight="1">
+    <row r="20" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
@@ -2895,7 +2898,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="11" customHeight="1">
+    <row r="21" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>18</v>
       </c>
@@ -2952,7 +2955,7 @@
       </c>
       <c r="S21" s="6"/>
     </row>
-    <row r="22" spans="1:19" ht="11" customHeight="1">
+    <row r="22" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>18</v>
       </c>
@@ -3009,7 +3012,7 @@
       </c>
       <c r="S22" s="6"/>
     </row>
-    <row r="23" spans="1:19" ht="11" customHeight="1">
+    <row r="23" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>18</v>
       </c>
@@ -3068,7 +3071,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="11" customHeight="1">
+    <row r="24" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>18</v>
       </c>
@@ -3125,7 +3128,7 @@
       </c>
       <c r="S24" s="6"/>
     </row>
-    <row r="25" spans="1:19" ht="11" customHeight="1">
+    <row r="25" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>18</v>
       </c>
@@ -3182,7 +3185,7 @@
       </c>
       <c r="S25" s="6"/>
     </row>
-    <row r="26" spans="1:19" ht="11" customHeight="1">
+    <row r="26" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>18</v>
       </c>
@@ -3239,7 +3242,7 @@
       </c>
       <c r="S26" s="6"/>
     </row>
-    <row r="27" spans="1:19" ht="11" customHeight="1">
+    <row r="27" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>18</v>
       </c>
@@ -3298,7 +3301,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="11" customHeight="1">
+    <row r="28" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>18</v>
       </c>
@@ -3357,7 +3360,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="11" customHeight="1">
+    <row r="29" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3407,7 +3410,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="11" customHeight="1">
+    <row r="30" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>18</v>
       </c>
@@ -3457,7 +3460,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="11" customHeight="1">
+    <row r="31" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>18</v>
       </c>
@@ -3514,7 +3517,7 @@
       </c>
       <c r="S31" s="6"/>
     </row>
-    <row r="32" spans="1:19" ht="11" customHeight="1">
+    <row r="32" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>18</v>
       </c>
@@ -3571,7 +3574,7 @@
       </c>
       <c r="S32" s="6"/>
     </row>
-    <row r="33" spans="1:19" ht="11" customHeight="1">
+    <row r="33" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>18</v>
       </c>
@@ -3630,7 +3633,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="11" customHeight="1">
+    <row r="34" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>18</v>
       </c>
@@ -3689,7 +3692,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="11" customHeight="1">
+    <row r="35" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>18</v>
       </c>
@@ -3748,7 +3751,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="36" spans="1:19" ht="11" customHeight="1">
+    <row r="36" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>18</v>
       </c>
@@ -3805,7 +3808,7 @@
       </c>
       <c r="S36" s="6"/>
     </row>
-    <row r="37" spans="1:19" ht="11" customHeight="1">
+    <row r="37" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>18</v>
       </c>
@@ -3864,7 +3867,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="11" customHeight="1">
+    <row r="38" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>18</v>
       </c>
@@ -3923,7 +3926,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="11" customHeight="1">
+    <row r="39" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>18</v>
       </c>
@@ -3982,7 +3985,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:19" ht="11" customHeight="1">
+    <row r="40" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>18</v>
       </c>
@@ -4039,7 +4042,7 @@
       </c>
       <c r="S40" s="6"/>
     </row>
-    <row r="41" spans="1:19" ht="11" customHeight="1">
+    <row r="41" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>18</v>
       </c>
@@ -4098,7 +4101,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="42" spans="1:19" ht="11" customHeight="1">
+    <row r="42" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>18</v>
       </c>
@@ -4155,7 +4158,7 @@
       </c>
       <c r="S42" s="6"/>
     </row>
-    <row r="43" spans="1:19" ht="11" customHeight="1">
+    <row r="43" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>18</v>
       </c>
@@ -4212,7 +4215,7 @@
       </c>
       <c r="S43" s="6"/>
     </row>
-    <row r="44" spans="1:19" ht="11" customHeight="1">
+    <row r="44" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>18</v>
       </c>
@@ -4271,7 +4274,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="1:19" ht="11" customHeight="1">
+    <row r="45" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>18</v>
       </c>
@@ -4321,7 +4324,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="46" spans="1:19" ht="11" customHeight="1">
+    <row r="46" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>18</v>
       </c>
@@ -4378,7 +4381,7 @@
       </c>
       <c r="S46" s="6"/>
     </row>
-    <row r="47" spans="1:19" ht="11" customHeight="1">
+    <row r="47" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>18</v>
       </c>
@@ -4435,7 +4438,7 @@
       </c>
       <c r="S47" s="6"/>
     </row>
-    <row r="48" spans="1:19" ht="11" customHeight="1">
+    <row r="48" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>18</v>
       </c>
@@ -4494,7 +4497,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:19" ht="11" customHeight="1">
+    <row r="49" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>18</v>
       </c>
@@ -4553,7 +4556,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:19" ht="11" customHeight="1">
+    <row r="50" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>18</v>
       </c>
@@ -4610,7 +4613,7 @@
       </c>
       <c r="S50" s="6"/>
     </row>
-    <row r="51" spans="1:19" ht="11" customHeight="1">
+    <row r="51" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>18</v>
       </c>
@@ -4660,7 +4663,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:19" ht="11" customHeight="1">
+    <row r="52" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>18</v>
       </c>
@@ -4719,7 +4722,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="53" spans="1:19" ht="11" customHeight="1">
+    <row r="53" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>18</v>
       </c>
@@ -4776,7 +4779,7 @@
       </c>
       <c r="S53" s="6"/>
     </row>
-    <row r="54" spans="1:19" ht="11" customHeight="1">
+    <row r="54" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>18</v>
       </c>
@@ -4833,7 +4836,7 @@
       </c>
       <c r="S54" s="6"/>
     </row>
-    <row r="55" spans="1:19" ht="11" customHeight="1">
+    <row r="55" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>18</v>
       </c>
@@ -4890,7 +4893,7 @@
       </c>
       <c r="S55" s="6"/>
     </row>
-    <row r="56" spans="1:19" ht="11" customHeight="1">
+    <row r="56" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>18</v>
       </c>
@@ -4947,7 +4950,7 @@
       </c>
       <c r="S56" s="6"/>
     </row>
-    <row r="57" spans="1:19" ht="11" customHeight="1">
+    <row r="57" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>18</v>
       </c>
@@ -5004,7 +5007,7 @@
       </c>
       <c r="S57" s="6"/>
     </row>
-    <row r="58" spans="1:19" ht="11" customHeight="1">
+    <row r="58" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>18</v>
       </c>
@@ -5063,7 +5066,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:19" ht="11" customHeight="1">
+    <row r="59" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>18</v>
       </c>
@@ -5120,7 +5123,7 @@
       </c>
       <c r="S59" s="6"/>
     </row>
-    <row r="60" spans="1:19" ht="11" customHeight="1">
+    <row r="60" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>18</v>
       </c>
@@ -5179,7 +5182,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" spans="1:19" ht="11" customHeight="1">
+    <row r="61" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>18</v>
       </c>
@@ -5236,7 +5239,7 @@
       </c>
       <c r="S61" s="6"/>
     </row>
-    <row r="62" spans="1:19" ht="11" customHeight="1">
+    <row r="62" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>18</v>
       </c>
@@ -5295,7 +5298,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:19" ht="11" customHeight="1">
+    <row r="63" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>18</v>
       </c>
@@ -5345,7 +5348,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="64" spans="1:19" ht="11" customHeight="1">
+    <row r="64" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>18</v>
       </c>
@@ -5402,7 +5405,7 @@
       </c>
       <c r="S64" s="6"/>
     </row>
-    <row r="65" spans="1:19" ht="11" customHeight="1">
+    <row r="65" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>18</v>
       </c>
@@ -5459,7 +5462,7 @@
       </c>
       <c r="S65" s="6"/>
     </row>
-    <row r="66" spans="1:19" ht="11" customHeight="1">
+    <row r="66" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>18</v>
       </c>
@@ -5518,7 +5521,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="11" customHeight="1">
+    <row r="67" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>18</v>
       </c>
@@ -5575,7 +5578,7 @@
       </c>
       <c r="S67" s="6"/>
     </row>
-    <row r="68" spans="1:19" ht="11" customHeight="1">
+    <row r="68" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>18</v>
       </c>
@@ -5632,7 +5635,7 @@
       </c>
       <c r="S68" s="6"/>
     </row>
-    <row r="69" spans="1:19" ht="11" customHeight="1">
+    <row r="69" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>18</v>
       </c>
@@ -5682,7 +5685,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="70" spans="1:19" ht="11" customHeight="1">
+    <row r="70" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>18</v>
       </c>
@@ -5739,7 +5742,7 @@
       </c>
       <c r="S70" s="6"/>
     </row>
-    <row r="71" spans="1:19" ht="11" customHeight="1">
+    <row r="71" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>18</v>
       </c>
@@ -5789,7 +5792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="72" spans="1:19" ht="11" customHeight="1">
+    <row r="72" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>18</v>
       </c>
@@ -5839,7 +5842,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="11" customHeight="1">
+    <row r="73" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>18</v>
       </c>
@@ -5889,7 +5892,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="11" customHeight="1">
+    <row r="74" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>18</v>
       </c>
@@ -5946,7 +5949,7 @@
       </c>
       <c r="S74" s="6"/>
     </row>
-    <row r="75" spans="1:19" ht="11" customHeight="1">
+    <row r="75" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>18</v>
       </c>
@@ -5996,7 +5999,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="76" spans="1:19" ht="11" customHeight="1">
+    <row r="76" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>18</v>
       </c>
@@ -6055,7 +6058,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="11" customHeight="1">
+    <row r="77" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>18</v>
       </c>
@@ -6112,7 +6115,7 @@
       </c>
       <c r="S77" s="6"/>
     </row>
-    <row r="78" spans="1:19" ht="11" customHeight="1">
+    <row r="78" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>18</v>
       </c>
@@ -6162,7 +6165,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="79" spans="1:19" ht="11" customHeight="1">
+    <row r="79" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>18</v>
       </c>
@@ -6219,7 +6222,7 @@
       </c>
       <c r="S79" s="6"/>
     </row>
-    <row r="80" spans="1:19" ht="11" customHeight="1">
+    <row r="80" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>18</v>
       </c>
@@ -6269,7 +6272,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="11" customHeight="1">
+    <row r="81" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>18</v>
       </c>
@@ -6326,7 +6329,7 @@
       </c>
       <c r="S81" s="6"/>
     </row>
-    <row r="82" spans="1:19" ht="11" customHeight="1">
+    <row r="82" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>18</v>
       </c>
@@ -6383,7 +6386,7 @@
       </c>
       <c r="S82" s="6"/>
     </row>
-    <row r="83" spans="1:19" ht="11" customHeight="1">
+    <row r="83" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>18</v>
       </c>
@@ -6442,7 +6445,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="84" spans="1:19" ht="11" customHeight="1">
+    <row r="84" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>18</v>
       </c>
@@ -6492,7 +6495,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="85" spans="1:19" ht="11" customHeight="1">
+    <row r="85" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>18</v>
       </c>
@@ -6542,7 +6545,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="86" spans="1:19" ht="11" customHeight="1">
+    <row r="86" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>18</v>
       </c>
@@ -6601,7 +6604,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:19" ht="11" customHeight="1">
+    <row r="87" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>18</v>
       </c>
@@ -6658,7 +6661,7 @@
       </c>
       <c r="S87" s="6"/>
     </row>
-    <row r="88" spans="1:19" ht="11" customHeight="1">
+    <row r="88" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>18</v>
       </c>
@@ -6708,7 +6711,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="11" customHeight="1">
+    <row r="89" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>18</v>
       </c>
@@ -6767,7 +6770,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" spans="1:19" ht="11" customHeight="1">
+    <row r="90" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>18</v>
       </c>
@@ -6817,7 +6820,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="91" spans="1:19" ht="11" customHeight="1">
+    <row r="91" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>18</v>
       </c>
@@ -6876,7 +6879,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:19" ht="11" customHeight="1">
+    <row r="92" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>18</v>
       </c>
@@ -6935,7 +6938,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:19" ht="11" customHeight="1">
+    <row r="93" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A93" s="4" t="s">
         <v>18</v>
       </c>
@@ -6994,7 +6997,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" spans="1:19" ht="11" customHeight="1">
+    <row r="94" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A94" s="4" t="s">
         <v>18</v>
       </c>
@@ -7051,7 +7054,7 @@
       </c>
       <c r="S94" s="6"/>
     </row>
-    <row r="95" spans="1:19" ht="11" customHeight="1">
+    <row r="95" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A95" s="4" t="s">
         <v>18</v>
       </c>
@@ -7110,7 +7113,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="96" spans="1:19" ht="11" customHeight="1">
+    <row r="96" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A96" s="4" t="s">
         <v>18</v>
       </c>
@@ -7169,7 +7172,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="97" spans="1:19" ht="11" customHeight="1">
+    <row r="97" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A97" s="4" t="s">
         <v>18</v>
       </c>
@@ -7226,7 +7229,7 @@
       </c>
       <c r="S97" s="6"/>
     </row>
-    <row r="98" spans="1:19" ht="11" customHeight="1">
+    <row r="98" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>18</v>
       </c>
@@ -7285,7 +7288,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:19" ht="11" customHeight="1">
+    <row r="99" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A99" s="4" t="s">
         <v>18</v>
       </c>
@@ -7344,7 +7347,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="100" spans="1:19" ht="11" customHeight="1">
+    <row r="100" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>18</v>
       </c>
@@ -7403,7 +7406,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="101" spans="1:19" ht="11" customHeight="1">
+    <row r="101" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>18</v>
       </c>
@@ -7462,7 +7465,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="102" spans="1:19" ht="11" customHeight="1">
+    <row r="102" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A102" s="4" t="s">
         <v>18</v>
       </c>
@@ -7519,7 +7522,7 @@
       </c>
       <c r="S102" s="6"/>
     </row>
-    <row r="103" spans="1:19" ht="11" customHeight="1">
+    <row r="103" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>18</v>
       </c>
@@ -7576,7 +7579,7 @@
       </c>
       <c r="S103" s="6"/>
     </row>
-    <row r="104" spans="1:19" ht="11" customHeight="1">
+    <row r="104" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A104" s="4" t="s">
         <v>18</v>
       </c>
@@ -7626,7 +7629,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:19" ht="11" customHeight="1">
+    <row r="105" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A105" s="4" t="s">
         <v>18</v>
       </c>
@@ -7683,7 +7686,7 @@
       </c>
       <c r="S105" s="6"/>
     </row>
-    <row r="106" spans="1:19" ht="11" customHeight="1">
+    <row r="106" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A106" s="4" t="s">
         <v>18</v>
       </c>
@@ -7740,7 +7743,7 @@
       </c>
       <c r="S106" s="6"/>
     </row>
-    <row r="107" spans="1:19" ht="11" customHeight="1">
+    <row r="107" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A107" s="4" t="s">
         <v>18</v>
       </c>
@@ -7797,7 +7800,7 @@
       </c>
       <c r="S107" s="6"/>
     </row>
-    <row r="108" spans="1:19" ht="11" customHeight="1">
+    <row r="108" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A108" s="4" t="s">
         <v>18</v>
       </c>
@@ -7854,7 +7857,7 @@
       </c>
       <c r="S108" s="6"/>
     </row>
-    <row r="109" spans="1:19" ht="11" customHeight="1">
+    <row r="109" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A109" s="4" t="s">
         <v>18</v>
       </c>
@@ -7913,7 +7916,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="110" spans="1:19" ht="11" customHeight="1">
+    <row r="110" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A110" s="4" t="s">
         <v>18</v>
       </c>
@@ -7970,7 +7973,7 @@
       </c>
       <c r="S110" s="6"/>
     </row>
-    <row r="111" spans="1:19" ht="11" customHeight="1">
+    <row r="111" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A111" s="4" t="s">
         <v>18</v>
       </c>
@@ -8020,7 +8023,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="112" spans="1:19" ht="11" customHeight="1">
+    <row r="112" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A112" s="4" t="s">
         <v>18</v>
       </c>
@@ -8079,7 +8082,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="113" spans="1:19" ht="11" customHeight="1">
+    <row r="113" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A113" s="4" t="s">
         <v>18</v>
       </c>
@@ -8138,7 +8141,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="114" spans="1:19" ht="11" customHeight="1">
+    <row r="114" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A114" s="4" t="s">
         <v>18</v>
       </c>
@@ -8197,7 +8200,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="115" spans="1:19" ht="11" customHeight="1">
+    <row r="115" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A115" s="4" t="s">
         <v>18</v>
       </c>
@@ -8256,7 +8259,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="116" spans="1:19" ht="11" customHeight="1">
+    <row r="116" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A116" s="4" t="s">
         <v>18</v>
       </c>
@@ -8313,7 +8316,7 @@
       </c>
       <c r="S116" s="6"/>
     </row>
-    <row r="117" spans="1:19" ht="11" customHeight="1">
+    <row r="117" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A117" s="4" t="s">
         <v>18</v>
       </c>
@@ -8363,7 +8366,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="118" spans="1:19" ht="11" customHeight="1">
+    <row r="118" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A118" s="4" t="s">
         <v>18</v>
       </c>
@@ -8413,7 +8416,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="119" spans="1:19" ht="11" customHeight="1">
+    <row r="119" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A119" s="4" t="s">
         <v>18</v>
       </c>
@@ -8463,7 +8466,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="120" spans="1:19" ht="11" customHeight="1">
+    <row r="120" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A120" s="4" t="s">
         <v>18</v>
       </c>
@@ -8513,7 +8516,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="121" spans="1:19" ht="11" customHeight="1">
+    <row r="121" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A121" s="4" t="s">
         <v>18</v>
       </c>
@@ -8570,7 +8573,7 @@
       </c>
       <c r="S121" s="6"/>
     </row>
-    <row r="122" spans="1:19" ht="11" customHeight="1">
+    <row r="122" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A122" s="4" t="s">
         <v>18</v>
       </c>
@@ -8629,7 +8632,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:19" ht="11" customHeight="1">
+    <row r="123" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A123" s="4" t="s">
         <v>18</v>
       </c>
@@ -8686,7 +8689,7 @@
       </c>
       <c r="S123" s="6"/>
     </row>
-    <row r="124" spans="1:19" ht="11" customHeight="1">
+    <row r="124" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A124" s="4" t="s">
         <v>18</v>
       </c>
@@ -8743,7 +8746,7 @@
       </c>
       <c r="S124" s="6"/>
     </row>
-    <row r="125" spans="1:19" ht="11" customHeight="1">
+    <row r="125" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A125" s="4" t="s">
         <v>18</v>
       </c>
@@ -8793,7 +8796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="126" spans="1:19" ht="11" customHeight="1">
+    <row r="126" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A126" s="4" t="s">
         <v>18</v>
       </c>
@@ -8843,7 +8846,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="127" spans="1:19" ht="11" customHeight="1">
+    <row r="127" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A127" s="4" t="s">
         <v>18</v>
       </c>
@@ -8900,7 +8903,7 @@
       </c>
       <c r="S127" s="6"/>
     </row>
-    <row r="128" spans="1:19" ht="11" customHeight="1">
+    <row r="128" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A128" s="4" t="s">
         <v>18</v>
       </c>
@@ -8950,7 +8953,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="129" spans="1:19" ht="11" customHeight="1">
+    <row r="129" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A129" s="4" t="s">
         <v>18</v>
       </c>
@@ -9007,7 +9010,7 @@
       </c>
       <c r="S129" s="6"/>
     </row>
-    <row r="130" spans="1:19" ht="11" customHeight="1">
+    <row r="130" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A130" s="4" t="s">
         <v>18</v>
       </c>
@@ -9064,7 +9067,7 @@
       </c>
       <c r="S130" s="6"/>
     </row>
-    <row r="131" spans="1:19" ht="11" customHeight="1">
+    <row r="131" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A131" s="4" t="s">
         <v>18</v>
       </c>
@@ -9123,7 +9126,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" spans="1:19" ht="11" customHeight="1">
+    <row r="132" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A132" s="4" t="s">
         <v>18</v>
       </c>
@@ -9182,7 +9185,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="133" spans="1:19" ht="11" customHeight="1">
+    <row r="133" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A133" s="4" t="s">
         <v>18</v>
       </c>
@@ -9241,7 +9244,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="134" spans="1:19" ht="11" customHeight="1">
+    <row r="134" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A134" s="4" t="s">
         <v>18</v>
       </c>
@@ -9298,7 +9301,7 @@
       </c>
       <c r="S134" s="6"/>
     </row>
-    <row r="135" spans="1:19" ht="11" customHeight="1">
+    <row r="135" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A135" s="4" t="s">
         <v>18</v>
       </c>
@@ -9355,7 +9358,7 @@
       </c>
       <c r="S135" s="6"/>
     </row>
-    <row r="136" spans="1:19" ht="11" customHeight="1">
+    <row r="136" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A136" s="4" t="s">
         <v>18</v>
       </c>
@@ -9412,7 +9415,7 @@
       </c>
       <c r="S136" s="6"/>
     </row>
-    <row r="137" spans="1:19" ht="11" customHeight="1">
+    <row r="137" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A137" s="4" t="s">
         <v>18</v>
       </c>
@@ -9469,7 +9472,7 @@
       </c>
       <c r="S137" s="6"/>
     </row>
-    <row r="138" spans="1:19" ht="11" customHeight="1">
+    <row r="138" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A138" s="4" t="s">
         <v>18</v>
       </c>
@@ -9528,7 +9531,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="139" spans="1:19" ht="11" customHeight="1">
+    <row r="139" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A139" s="4" t="s">
         <v>18</v>
       </c>
@@ -9585,7 +9588,7 @@
       </c>
       <c r="S139" s="6"/>
     </row>
-    <row r="140" spans="1:19" ht="11" customHeight="1">
+    <row r="140" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A140" s="4" t="s">
         <v>18</v>
       </c>
@@ -9635,7 +9638,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="11" customHeight="1">
+    <row r="141" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A141" s="4" t="s">
         <v>18</v>
       </c>
@@ -9694,7 +9697,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="142" spans="1:19" ht="11" customHeight="1">
+    <row r="142" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A142" s="4" t="s">
         <v>18</v>
       </c>
@@ -9751,7 +9754,7 @@
       </c>
       <c r="S142" s="6"/>
     </row>
-    <row r="143" spans="1:19" ht="11" customHeight="1">
+    <row r="143" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A143" s="4" t="s">
         <v>18</v>
       </c>
@@ -9808,7 +9811,7 @@
       </c>
       <c r="S143" s="6"/>
     </row>
-    <row r="144" spans="1:19" ht="11" customHeight="1">
+    <row r="144" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A144" s="4" t="s">
         <v>18</v>
       </c>
@@ -9867,7 +9870,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="145" spans="1:19" ht="11" customHeight="1">
+    <row r="145" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A145" s="4" t="s">
         <v>18</v>
       </c>
@@ -9926,7 +9929,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="146" spans="1:19" ht="11" customHeight="1">
+    <row r="146" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A146" s="4" t="s">
         <v>18</v>
       </c>
@@ -9983,7 +9986,7 @@
       </c>
       <c r="S146" s="6"/>
     </row>
-    <row r="147" spans="1:19" ht="11" customHeight="1">
+    <row r="147" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A147" s="4" t="s">
         <v>18</v>
       </c>
@@ -10040,7 +10043,7 @@
       </c>
       <c r="S147" s="6"/>
     </row>
-    <row r="148" spans="1:19" ht="11" customHeight="1">
+    <row r="148" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A148" s="4" t="s">
         <v>18</v>
       </c>
@@ -10099,7 +10102,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="149" spans="1:19" ht="11" customHeight="1">
+    <row r="149" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A149" s="4" t="s">
         <v>18</v>
       </c>
@@ -10156,7 +10159,7 @@
       </c>
       <c r="S149" s="6"/>
     </row>
-    <row r="150" spans="1:19" ht="11" customHeight="1">
+    <row r="150" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A150" s="4" t="s">
         <v>18</v>
       </c>
@@ -10213,7 +10216,7 @@
       </c>
       <c r="S150" s="6"/>
     </row>
-    <row r="151" spans="1:19" ht="11" customHeight="1">
+    <row r="151" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A151" s="4" t="s">
         <v>78</v>
       </c>
@@ -10272,7 +10275,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="152" spans="1:19" ht="11" customHeight="1">
+    <row r="152" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A152" s="4" t="s">
         <v>78</v>
       </c>
@@ -10329,7 +10332,7 @@
       </c>
       <c r="S152" s="6"/>
     </row>
-    <row r="153" spans="1:19" ht="11" customHeight="1">
+    <row r="153" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A153" s="4" t="s">
         <v>78</v>
       </c>
@@ -10386,7 +10389,7 @@
       </c>
       <c r="S153" s="6"/>
     </row>
-    <row r="154" spans="1:19" ht="11" customHeight="1">
+    <row r="154" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A154" s="4" t="s">
         <v>78</v>
       </c>
@@ -10445,7 +10448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="155" spans="1:19" ht="11" customHeight="1">
+    <row r="155" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A155" s="4" t="s">
         <v>78</v>
       </c>
@@ -10504,7 +10507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="156" spans="1:19" ht="11" customHeight="1">
+    <row r="156" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A156" s="4" t="s">
         <v>78</v>
       </c>
@@ -10563,7 +10566,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="157" spans="1:19" ht="11" customHeight="1">
+    <row r="157" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A157" s="4" t="s">
         <v>78</v>
       </c>
@@ -10620,7 +10623,7 @@
       </c>
       <c r="S157" s="6"/>
     </row>
-    <row r="158" spans="1:19" ht="11" customHeight="1">
+    <row r="158" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A158" s="4" t="s">
         <v>78</v>
       </c>
@@ -10677,7 +10680,7 @@
       </c>
       <c r="S158" s="6"/>
     </row>
-    <row r="159" spans="1:19" ht="11" customHeight="1">
+    <row r="159" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A159" s="4" t="s">
         <v>78</v>
       </c>
@@ -10736,7 +10739,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="160" spans="1:19" ht="11" customHeight="1">
+    <row r="160" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A160" s="4" t="s">
         <v>78</v>
       </c>
@@ -10795,7 +10798,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:19" ht="11" customHeight="1">
+    <row r="161" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A161" s="4" t="s">
         <v>78</v>
       </c>
@@ -10852,7 +10855,7 @@
       </c>
       <c r="S161" s="6"/>
     </row>
-    <row r="162" spans="1:19" ht="11" customHeight="1">
+    <row r="162" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A162" s="4" t="s">
         <v>78</v>
       </c>
@@ -10911,7 +10914,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:19" ht="11" customHeight="1">
+    <row r="163" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A163" s="4" t="s">
         <v>78</v>
       </c>
@@ -10970,7 +10973,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="164" spans="1:19" ht="11" customHeight="1">
+    <row r="164" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A164" s="4" t="s">
         <v>78</v>
       </c>
@@ -11029,7 +11032,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="165" spans="1:19" ht="11" customHeight="1">
+    <row r="165" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A165" s="4" t="s">
         <v>78</v>
       </c>
@@ -11088,7 +11091,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="166" spans="1:19" ht="11" customHeight="1">
+    <row r="166" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A166" s="4" t="s">
         <v>78</v>
       </c>
@@ -11145,7 +11148,7 @@
       </c>
       <c r="S166" s="6"/>
     </row>
-    <row r="167" spans="1:19" ht="11" customHeight="1">
+    <row r="167" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A167" s="4" t="s">
         <v>78</v>
       </c>
@@ -11204,7 +11207,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="168" spans="1:19" ht="11" customHeight="1">
+    <row r="168" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A168" s="4" t="s">
         <v>78</v>
       </c>
@@ -11263,7 +11266,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="169" spans="1:19" ht="11" customHeight="1">
+    <row r="169" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A169" s="4" t="s">
         <v>78</v>
       </c>
@@ -11322,7 +11325,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="170" spans="1:19" ht="11" customHeight="1">
+    <row r="170" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A170" s="4" t="s">
         <v>78</v>
       </c>
@@ -11381,7 +11384,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="171" spans="1:19" ht="11" customHeight="1">
+    <row r="171" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A171" s="4" t="s">
         <v>78</v>
       </c>
@@ -11440,7 +11443,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="172" spans="1:19" ht="11" customHeight="1">
+    <row r="172" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A172" s="4" t="s">
         <v>78</v>
       </c>
@@ -11497,7 +11500,7 @@
       </c>
       <c r="S172" s="6"/>
     </row>
-    <row r="173" spans="1:19" ht="11" customHeight="1">
+    <row r="173" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A173" s="4" t="s">
         <v>78</v>
       </c>
@@ -11547,7 +11550,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="174" spans="1:19" ht="11" customHeight="1">
+    <row r="174" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A174" s="4" t="s">
         <v>78</v>
       </c>
@@ -11604,7 +11607,7 @@
       </c>
       <c r="S174" s="6"/>
     </row>
-    <row r="175" spans="1:19" ht="11" customHeight="1">
+    <row r="175" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A175" s="4" t="s">
         <v>78</v>
       </c>
@@ -11663,7 +11666,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="176" spans="1:19" ht="11" customHeight="1">
+    <row r="176" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A176" s="4" t="s">
         <v>78</v>
       </c>
@@ -11722,7 +11725,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="177" spans="1:19" ht="11" customHeight="1">
+    <row r="177" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A177" s="4" t="s">
         <v>78</v>
       </c>
@@ -11781,7 +11784,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="178" spans="1:19" ht="11" customHeight="1">
+    <row r="178" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A178" s="4" t="s">
         <v>78</v>
       </c>
@@ -11840,7 +11843,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="179" spans="1:19" ht="11" customHeight="1">
+    <row r="179" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A179" s="4" t="s">
         <v>78</v>
       </c>
@@ -11890,7 +11893,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="180" spans="1:19" ht="11" customHeight="1">
+    <row r="180" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A180" s="4" t="s">
         <v>78</v>
       </c>
@@ -11949,7 +11952,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="181" spans="1:19" ht="11" customHeight="1">
+    <row r="181" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A181" s="4" t="s">
         <v>78</v>
       </c>
@@ -12008,7 +12011,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:19" ht="11" customHeight="1">
+    <row r="182" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A182" s="4" t="s">
         <v>78</v>
       </c>
@@ -12065,7 +12068,7 @@
       </c>
       <c r="S182" s="6"/>
     </row>
-    <row r="183" spans="1:19" ht="11" customHeight="1">
+    <row r="183" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A183" s="4" t="s">
         <v>78</v>
       </c>
@@ -12122,7 +12125,7 @@
       </c>
       <c r="S183" s="6"/>
     </row>
-    <row r="184" spans="1:19" ht="11" customHeight="1">
+    <row r="184" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A184" s="4" t="s">
         <v>78</v>
       </c>
@@ -12172,7 +12175,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="185" spans="1:19" ht="11" customHeight="1">
+    <row r="185" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A185" s="4" t="s">
         <v>78</v>
       </c>
@@ -12229,7 +12232,7 @@
       </c>
       <c r="S185" s="6"/>
     </row>
-    <row r="186" spans="1:19" ht="11" customHeight="1">
+    <row r="186" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A186" s="4" t="s">
         <v>78</v>
       </c>
@@ -12286,7 +12289,7 @@
       </c>
       <c r="S186" s="6"/>
     </row>
-    <row r="187" spans="1:19" ht="11" customHeight="1">
+    <row r="187" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A187" s="4" t="s">
         <v>78</v>
       </c>
@@ -12343,7 +12346,7 @@
       </c>
       <c r="S187" s="6"/>
     </row>
-    <row r="188" spans="1:19" ht="11" customHeight="1">
+    <row r="188" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A188" s="4" t="s">
         <v>78</v>
       </c>
@@ -12400,7 +12403,7 @@
       </c>
       <c r="S188" s="6"/>
     </row>
-    <row r="189" spans="1:19" ht="11" customHeight="1">
+    <row r="189" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A189" s="4" t="s">
         <v>78</v>
       </c>
@@ -12457,7 +12460,7 @@
       </c>
       <c r="S189" s="6"/>
     </row>
-    <row r="190" spans="1:19" ht="11" customHeight="1">
+    <row r="190" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A190" s="4" t="s">
         <v>78</v>
       </c>
@@ -12514,7 +12517,7 @@
       </c>
       <c r="S190" s="6"/>
     </row>
-    <row r="191" spans="1:19" ht="11" customHeight="1">
+    <row r="191" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A191" s="4" t="s">
         <v>78</v>
       </c>
@@ -12573,7 +12576,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="192" spans="1:19" ht="11" customHeight="1">
+    <row r="192" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A192" s="4" t="s">
         <v>78</v>
       </c>
@@ -12630,7 +12633,7 @@
       </c>
       <c r="S192" s="6"/>
     </row>
-    <row r="193" spans="1:19" ht="11" customHeight="1">
+    <row r="193" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A193" s="4" t="s">
         <v>78</v>
       </c>
@@ -12687,7 +12690,7 @@
       </c>
       <c r="S193" s="6"/>
     </row>
-    <row r="194" spans="1:19" ht="11" customHeight="1">
+    <row r="194" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A194" s="4" t="s">
         <v>78</v>
       </c>
@@ -12744,7 +12747,7 @@
       </c>
       <c r="S194" s="6"/>
     </row>
-    <row r="195" spans="1:19" ht="11" customHeight="1">
+    <row r="195" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A195" s="4" t="s">
         <v>78</v>
       </c>
@@ -12801,7 +12804,7 @@
       </c>
       <c r="S195" s="6"/>
     </row>
-    <row r="196" spans="1:19" ht="11" customHeight="1">
+    <row r="196" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A196" s="4" t="s">
         <v>78</v>
       </c>
@@ -12860,7 +12863,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="197" spans="1:19" ht="11" customHeight="1">
+    <row r="197" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A197" s="4" t="s">
         <v>78</v>
       </c>
@@ -12919,7 +12922,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="198" spans="1:19" ht="11" customHeight="1">
+    <row r="198" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A198" s="4" t="s">
         <v>78</v>
       </c>
@@ -12978,7 +12981,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="199" spans="1:19" ht="11" customHeight="1">
+    <row r="199" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A199" s="4" t="s">
         <v>78</v>
       </c>
@@ -13035,7 +13038,7 @@
       </c>
       <c r="S199" s="6"/>
     </row>
-    <row r="200" spans="1:19" ht="11" customHeight="1">
+    <row r="200" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A200" s="4" t="s">
         <v>78</v>
       </c>
@@ -13092,7 +13095,7 @@
       </c>
       <c r="S200" s="6"/>
     </row>
-    <row r="201" spans="1:19" ht="11" customHeight="1">
+    <row r="201" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A201" s="4" t="s">
         <v>78</v>
       </c>
@@ -13149,7 +13152,7 @@
       </c>
       <c r="S201" s="6"/>
     </row>
-    <row r="202" spans="1:19" ht="11" customHeight="1">
+    <row r="202" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A202" s="4" t="s">
         <v>78</v>
       </c>
@@ -13208,7 +13211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="203" spans="1:19" ht="11" customHeight="1">
+    <row r="203" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A203" s="4" t="s">
         <v>78</v>
       </c>
@@ -13267,7 +13270,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="204" spans="1:19" ht="11" customHeight="1">
+    <row r="204" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A204" s="4" t="s">
         <v>78</v>
       </c>
@@ -13324,7 +13327,7 @@
       </c>
       <c r="S204" s="6"/>
     </row>
-    <row r="205" spans="1:19" ht="11" customHeight="1">
+    <row r="205" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A205" s="4" t="s">
         <v>78</v>
       </c>
@@ -13381,7 +13384,7 @@
       </c>
       <c r="S205" s="6"/>
     </row>
-    <row r="206" spans="1:19" ht="11" customHeight="1">
+    <row r="206" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A206" s="4" t="s">
         <v>78</v>
       </c>
@@ -13440,7 +13443,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="207" spans="1:19" ht="11" customHeight="1">
+    <row r="207" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A207" s="4" t="s">
         <v>78</v>
       </c>
@@ -13497,7 +13500,7 @@
       </c>
       <c r="S207" s="6"/>
     </row>
-    <row r="208" spans="1:19" ht="11" customHeight="1">
+    <row r="208" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A208" s="4" t="s">
         <v>78</v>
       </c>
@@ -13554,7 +13557,7 @@
       </c>
       <c r="S208" s="6"/>
     </row>
-    <row r="209" spans="1:19" ht="11" customHeight="1">
+    <row r="209" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A209" s="4" t="s">
         <v>78</v>
       </c>
@@ -13611,7 +13614,7 @@
       </c>
       <c r="S209" s="6"/>
     </row>
-    <row r="210" spans="1:19" ht="11" customHeight="1">
+    <row r="210" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A210" s="4" t="s">
         <v>78</v>
       </c>
@@ -13670,7 +13673,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="211" spans="1:19" ht="11" customHeight="1">
+    <row r="211" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A211" s="4" t="s">
         <v>78</v>
       </c>
@@ -13727,7 +13730,7 @@
       </c>
       <c r="S211" s="6"/>
     </row>
-    <row r="212" spans="1:19" ht="11" customHeight="1">
+    <row r="212" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A212" s="4" t="s">
         <v>78</v>
       </c>
@@ -13786,7 +13789,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="213" spans="1:19" ht="11" customHeight="1">
+    <row r="213" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A213" s="4" t="s">
         <v>78</v>
       </c>
@@ -13845,7 +13848,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="214" spans="1:19" ht="11" customHeight="1">
+    <row r="214" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A214" s="4" t="s">
         <v>78</v>
       </c>
@@ -13902,7 +13905,7 @@
       </c>
       <c r="S214" s="6"/>
     </row>
-    <row r="215" spans="1:19" ht="11" customHeight="1">
+    <row r="215" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A215" s="4" t="s">
         <v>78</v>
       </c>
@@ -13961,7 +13964,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="216" spans="1:19" ht="11" customHeight="1">
+    <row r="216" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A216" s="4" t="s">
         <v>78</v>
       </c>
@@ -14018,7 +14021,7 @@
       </c>
       <c r="S216" s="6"/>
     </row>
-    <row r="217" spans="1:19" ht="11" customHeight="1">
+    <row r="217" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A217" s="4" t="s">
         <v>78</v>
       </c>
@@ -14075,7 +14078,7 @@
       </c>
       <c r="S217" s="6"/>
     </row>
-    <row r="218" spans="1:19" ht="11" customHeight="1">
+    <row r="218" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A218" s="4" t="s">
         <v>78</v>
       </c>
@@ -14132,7 +14135,7 @@
       </c>
       <c r="S218" s="6"/>
     </row>
-    <row r="219" spans="1:19" ht="11" customHeight="1">
+    <row r="219" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A219" s="4" t="s">
         <v>78</v>
       </c>
@@ -14191,7 +14194,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="220" spans="1:19" ht="11" customHeight="1">
+    <row r="220" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A220" s="4" t="s">
         <v>78</v>
       </c>
@@ -14250,7 +14253,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="221" spans="1:19" ht="11" customHeight="1">
+    <row r="221" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A221" s="4" t="s">
         <v>78</v>
       </c>
@@ -14307,7 +14310,7 @@
       </c>
       <c r="S221" s="6"/>
     </row>
-    <row r="222" spans="1:19" ht="11" customHeight="1">
+    <row r="222" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A222" s="4" t="s">
         <v>78</v>
       </c>
@@ -14366,7 +14369,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="223" spans="1:19" ht="11" customHeight="1">
+    <row r="223" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A223" s="4" t="s">
         <v>78</v>
       </c>
@@ -14423,7 +14426,7 @@
       </c>
       <c r="S223" s="6"/>
     </row>
-    <row r="224" spans="1:19" ht="11" customHeight="1">
+    <row r="224" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A224" s="4" t="s">
         <v>78</v>
       </c>
@@ -14480,7 +14483,7 @@
       </c>
       <c r="S224" s="6"/>
     </row>
-    <row r="225" spans="1:19" ht="11" customHeight="1">
+    <row r="225" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A225" s="4" t="s">
         <v>78</v>
       </c>
@@ -14537,7 +14540,7 @@
       </c>
       <c r="S225" s="6"/>
     </row>
-    <row r="226" spans="1:19" ht="11" customHeight="1">
+    <row r="226" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A226" s="4" t="s">
         <v>78</v>
       </c>
@@ -14594,7 +14597,7 @@
       </c>
       <c r="S226" s="6"/>
     </row>
-    <row r="227" spans="1:19" ht="11" customHeight="1">
+    <row r="227" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A227" s="4" t="s">
         <v>78</v>
       </c>
@@ -14651,7 +14654,7 @@
       </c>
       <c r="S227" s="6"/>
     </row>
-    <row r="228" spans="1:19" ht="11" customHeight="1">
+    <row r="228" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A228" s="4" t="s">
         <v>78</v>
       </c>
@@ -14710,7 +14713,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="229" spans="1:19" ht="11" customHeight="1">
+    <row r="229" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A229" s="4" t="s">
         <v>78</v>
       </c>
@@ -14767,7 +14770,7 @@
       </c>
       <c r="S229" s="6"/>
     </row>
-    <row r="230" spans="1:19" ht="11" customHeight="1">
+    <row r="230" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A230" s="4" t="s">
         <v>78</v>
       </c>
@@ -14826,7 +14829,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="231" spans="1:19" ht="11" customHeight="1">
+    <row r="231" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A231" s="4" t="s">
         <v>78</v>
       </c>
@@ -14885,7 +14888,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="232" spans="1:19" ht="11" customHeight="1">
+    <row r="232" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A232" s="4" t="s">
         <v>78</v>
       </c>
@@ -14944,7 +14947,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="233" spans="1:19" ht="11" customHeight="1">
+    <row r="233" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A233" s="4" t="s">
         <v>78</v>
       </c>
@@ -15003,7 +15006,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="234" spans="1:19" ht="11" customHeight="1">
+    <row r="234" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A234" s="4" t="s">
         <v>78</v>
       </c>
@@ -15062,7 +15065,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="235" spans="1:19" ht="11" customHeight="1">
+    <row r="235" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A235" s="4" t="s">
         <v>78</v>
       </c>
@@ -15119,7 +15122,7 @@
       </c>
       <c r="S235" s="6"/>
     </row>
-    <row r="236" spans="1:19" ht="11" customHeight="1">
+    <row r="236" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A236" s="4" t="s">
         <v>78</v>
       </c>
@@ -15176,7 +15179,7 @@
       </c>
       <c r="S236" s="6"/>
     </row>
-    <row r="237" spans="1:19" ht="11" customHeight="1">
+    <row r="237" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A237" s="4" t="s">
         <v>78</v>
       </c>
@@ -15235,7 +15238,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="238" spans="1:19" ht="11" customHeight="1">
+    <row r="238" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A238" s="4" t="s">
         <v>78</v>
       </c>
@@ -15294,7 +15297,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="239" spans="1:19" ht="11" customHeight="1">
+    <row r="239" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A239" s="4" t="s">
         <v>78</v>
       </c>
@@ -15351,7 +15354,7 @@
       </c>
       <c r="S239" s="6"/>
     </row>
-    <row r="240" spans="1:19" ht="11" customHeight="1">
+    <row r="240" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A240" s="4" t="s">
         <v>78</v>
       </c>
@@ -15408,7 +15411,7 @@
       </c>
       <c r="S240" s="6"/>
     </row>
-    <row r="241" spans="1:19" ht="11" customHeight="1">
+    <row r="241" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A241" s="4" t="s">
         <v>78</v>
       </c>
@@ -15465,7 +15468,7 @@
       </c>
       <c r="S241" s="6"/>
     </row>
-    <row r="242" spans="1:19" ht="11" customHeight="1">
+    <row r="242" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A242" s="4" t="s">
         <v>78</v>
       </c>
@@ -15522,7 +15525,7 @@
       </c>
       <c r="S242" s="6"/>
     </row>
-    <row r="243" spans="1:19" ht="11" customHeight="1">
+    <row r="243" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A243" s="4" t="s">
         <v>78</v>
       </c>
@@ -15579,7 +15582,7 @@
       </c>
       <c r="S243" s="6"/>
     </row>
-    <row r="244" spans="1:19" ht="11" customHeight="1">
+    <row r="244" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A244" s="4" t="s">
         <v>78</v>
       </c>
@@ -15636,7 +15639,7 @@
       </c>
       <c r="S244" s="6"/>
     </row>
-    <row r="245" spans="1:19" ht="11" customHeight="1">
+    <row r="245" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A245" s="4" t="s">
         <v>78</v>
       </c>
@@ -15695,7 +15698,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="246" spans="1:19" ht="11" customHeight="1">
+    <row r="246" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A246" s="4" t="s">
         <v>78</v>
       </c>
@@ -15752,7 +15755,7 @@
       </c>
       <c r="S246" s="6"/>
     </row>
-    <row r="247" spans="1:19" ht="11" customHeight="1">
+    <row r="247" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A247" s="4" t="s">
         <v>78</v>
       </c>
@@ -15811,7 +15814,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="248" spans="1:19" ht="11" customHeight="1">
+    <row r="248" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A248" s="4" t="s">
         <v>78</v>
       </c>
@@ -15870,7 +15873,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="249" spans="1:19" ht="11" customHeight="1">
+    <row r="249" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A249" s="4" t="s">
         <v>78</v>
       </c>
@@ -15920,7 +15923,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="250" spans="1:19" ht="11" customHeight="1">
+    <row r="250" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A250" s="4" t="s">
         <v>78</v>
       </c>
@@ -15979,7 +15982,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:19" ht="11" customHeight="1">
+    <row r="251" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A251" s="4" t="s">
         <v>78</v>
       </c>
@@ -16038,7 +16041,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="252" spans="1:19" ht="11" customHeight="1">
+    <row r="252" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A252" s="4" t="s">
         <v>78</v>
       </c>
@@ -16097,7 +16100,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="253" spans="1:19" ht="11" customHeight="1">
+    <row r="253" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A253" s="4" t="s">
         <v>78</v>
       </c>
@@ -16154,7 +16157,7 @@
       </c>
       <c r="S253" s="6"/>
     </row>
-    <row r="254" spans="1:19" ht="11" customHeight="1">
+    <row r="254" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A254" s="4" t="s">
         <v>78</v>
       </c>
@@ -16213,7 +16216,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="255" spans="1:19" ht="11" customHeight="1">
+    <row r="255" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A255" s="4" t="s">
         <v>78</v>
       </c>
@@ -16270,7 +16273,7 @@
       </c>
       <c r="S255" s="6"/>
     </row>
-    <row r="256" spans="1:19" ht="11" customHeight="1">
+    <row r="256" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A256" s="4" t="s">
         <v>78</v>
       </c>
@@ -16327,7 +16330,7 @@
       </c>
       <c r="S256" s="6"/>
     </row>
-    <row r="257" spans="1:19" ht="11" customHeight="1">
+    <row r="257" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A257" s="4" t="s">
         <v>78</v>
       </c>
@@ -16377,7 +16380,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="258" spans="1:19" ht="11" customHeight="1">
+    <row r="258" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A258" s="4" t="s">
         <v>78</v>
       </c>
@@ -16434,7 +16437,7 @@
       </c>
       <c r="S258" s="6"/>
     </row>
-    <row r="259" spans="1:19" ht="11" customHeight="1">
+    <row r="259" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A259" s="4" t="s">
         <v>78</v>
       </c>
@@ -16491,7 +16494,7 @@
       </c>
       <c r="S259" s="6"/>
     </row>
-    <row r="260" spans="1:19" ht="11" customHeight="1">
+    <row r="260" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A260" s="4" t="s">
         <v>78</v>
       </c>
@@ -16550,7 +16553,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="261" spans="1:19" ht="11" customHeight="1">
+    <row r="261" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A261" s="4" t="s">
         <v>78</v>
       </c>
@@ -16609,7 +16612,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="262" spans="1:19" ht="11" customHeight="1">
+    <row r="262" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A262" s="4" t="s">
         <v>78</v>
       </c>
@@ -16668,7 +16671,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="263" spans="1:19" ht="11" customHeight="1">
+    <row r="263" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A263" s="4" t="s">
         <v>78</v>
       </c>
@@ -16725,7 +16728,7 @@
       </c>
       <c r="S263" s="6"/>
     </row>
-    <row r="264" spans="1:19" ht="11" customHeight="1">
+    <row r="264" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A264" s="4" t="s">
         <v>78</v>
       </c>
@@ -16782,7 +16785,7 @@
       </c>
       <c r="S264" s="6"/>
     </row>
-    <row r="265" spans="1:19" ht="11" customHeight="1">
+    <row r="265" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A265" s="4" t="s">
         <v>78</v>
       </c>
@@ -16839,7 +16842,7 @@
       </c>
       <c r="S265" s="6"/>
     </row>
-    <row r="266" spans="1:19" ht="11" customHeight="1">
+    <row r="266" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A266" s="4" t="s">
         <v>78</v>
       </c>
@@ -16898,7 +16901,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="267" spans="1:19" ht="11" customHeight="1">
+    <row r="267" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A267" s="4" t="s">
         <v>78</v>
       </c>
@@ -16955,7 +16958,7 @@
       </c>
       <c r="S267" s="6"/>
     </row>
-    <row r="268" spans="1:19" ht="11" customHeight="1">
+    <row r="268" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A268" s="4" t="s">
         <v>78</v>
       </c>
@@ -17012,7 +17015,7 @@
       </c>
       <c r="S268" s="6"/>
     </row>
-    <row r="269" spans="1:19" ht="11" customHeight="1">
+    <row r="269" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A269" s="4" t="s">
         <v>78</v>
       </c>
@@ -17071,7 +17074,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="270" spans="1:19" ht="11" customHeight="1">
+    <row r="270" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A270" s="4" t="s">
         <v>78</v>
       </c>
@@ -17128,7 +17131,7 @@
       </c>
       <c r="S270" s="6"/>
     </row>
-    <row r="271" spans="1:19" ht="11" customHeight="1">
+    <row r="271" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A271" s="4" t="s">
         <v>78</v>
       </c>
@@ -17185,7 +17188,7 @@
       </c>
       <c r="S271" s="6"/>
     </row>
-    <row r="272" spans="1:19" ht="11" customHeight="1">
+    <row r="272" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A272" s="4" t="s">
         <v>78</v>
       </c>
@@ -17242,7 +17245,7 @@
       </c>
       <c r="S272" s="6"/>
     </row>
-    <row r="273" spans="1:19" ht="11" customHeight="1">
+    <row r="273" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A273" s="4" t="s">
         <v>78</v>
       </c>
@@ -17299,7 +17302,7 @@
       </c>
       <c r="S273" s="6"/>
     </row>
-    <row r="274" spans="1:19" ht="11" customHeight="1">
+    <row r="274" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A274" s="4" t="s">
         <v>78</v>
       </c>
@@ -17358,7 +17361,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="275" spans="1:19" ht="11" customHeight="1">
+    <row r="275" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A275" s="4" t="s">
         <v>78</v>
       </c>
@@ -17417,7 +17420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:19" ht="11" customHeight="1">
+    <row r="276" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A276" s="4" t="s">
         <v>78</v>
       </c>
@@ -17476,7 +17479,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="277" spans="1:19" ht="11" customHeight="1">
+    <row r="277" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A277" s="4" t="s">
         <v>78</v>
       </c>
@@ -17535,7 +17538,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="278" spans="1:19" ht="11" customHeight="1">
+    <row r="278" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A278" s="4" t="s">
         <v>78</v>
       </c>
@@ -17592,7 +17595,7 @@
       </c>
       <c r="S278" s="6"/>
     </row>
-    <row r="279" spans="1:19" ht="11" customHeight="1">
+    <row r="279" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A279" s="4" t="s">
         <v>78</v>
       </c>
@@ -17649,7 +17652,7 @@
       </c>
       <c r="S279" s="6"/>
     </row>
-    <row r="280" spans="1:19" ht="11" customHeight="1">
+    <row r="280" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A280" s="4" t="s">
         <v>78</v>
       </c>
@@ -17706,7 +17709,7 @@
       </c>
       <c r="S280" s="6"/>
     </row>
-    <row r="281" spans="1:19" ht="11" customHeight="1">
+    <row r="281" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A281" s="4" t="s">
         <v>78</v>
       </c>
@@ -17765,7 +17768,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="282" spans="1:19" ht="11" customHeight="1">
+    <row r="282" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A282" s="4" t="s">
         <v>78</v>
       </c>
@@ -17822,7 +17825,7 @@
       </c>
       <c r="S282" s="6"/>
     </row>
-    <row r="283" spans="1:19" ht="11" customHeight="1">
+    <row r="283" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A283" s="4" t="s">
         <v>78</v>
       </c>
@@ -17881,7 +17884,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:19" ht="11" customHeight="1">
+    <row r="284" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A284" s="4" t="s">
         <v>78</v>
       </c>
@@ -17938,7 +17941,7 @@
       </c>
       <c r="S284" s="6"/>
     </row>
-    <row r="285" spans="1:19" ht="11" customHeight="1">
+    <row r="285" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A285" s="4" t="s">
         <v>78</v>
       </c>
@@ -17997,7 +18000,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="286" spans="1:19" ht="11" customHeight="1">
+    <row r="286" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A286" s="4" t="s">
         <v>78</v>
       </c>
@@ -18054,7 +18057,7 @@
       </c>
       <c r="S286" s="6"/>
     </row>
-    <row r="287" spans="1:19" ht="11" customHeight="1">
+    <row r="287" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A287" s="4" t="s">
         <v>113</v>
       </c>
@@ -18111,7 +18114,7 @@
       </c>
       <c r="S287" s="6"/>
     </row>
-    <row r="288" spans="1:19" ht="11" customHeight="1">
+    <row r="288" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A288" s="4" t="s">
         <v>113</v>
       </c>
@@ -18168,7 +18171,7 @@
       </c>
       <c r="S288" s="6"/>
     </row>
-    <row r="289" spans="1:19" ht="11" customHeight="1">
+    <row r="289" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A289" s="4" t="s">
         <v>113</v>
       </c>
@@ -18218,7 +18221,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="290" spans="1:19" ht="11" customHeight="1">
+    <row r="290" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A290" s="4" t="s">
         <v>113</v>
       </c>
@@ -18277,7 +18280,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:19" ht="11" customHeight="1">
+    <row r="291" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A291" s="4" t="s">
         <v>113</v>
       </c>
@@ -18336,7 +18339,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="292" spans="1:19" ht="11" customHeight="1">
+    <row r="292" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A292" s="4" t="s">
         <v>113</v>
       </c>
@@ -18393,7 +18396,7 @@
       </c>
       <c r="S292" s="6"/>
     </row>
-    <row r="293" spans="1:19" ht="11" customHeight="1">
+    <row r="293" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A293" s="4" t="s">
         <v>113</v>
       </c>
@@ -18450,7 +18453,7 @@
       </c>
       <c r="S293" s="6"/>
     </row>
-    <row r="294" spans="1:19" ht="11" customHeight="1">
+    <row r="294" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A294" s="4" t="s">
         <v>113</v>
       </c>
@@ -18507,7 +18510,7 @@
       </c>
       <c r="S294" s="6"/>
     </row>
-    <row r="295" spans="1:19" ht="11" customHeight="1">
+    <row r="295" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A295" s="4" t="s">
         <v>113</v>
       </c>
@@ -18564,7 +18567,7 @@
       </c>
       <c r="S295" s="6"/>
     </row>
-    <row r="296" spans="1:19" ht="11" customHeight="1">
+    <row r="296" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A296" s="4" t="s">
         <v>113</v>
       </c>
@@ -18614,7 +18617,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="297" spans="1:19" ht="11" customHeight="1">
+    <row r="297" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A297" s="4" t="s">
         <v>113</v>
       </c>
@@ -18671,7 +18674,7 @@
       </c>
       <c r="S297" s="6"/>
     </row>
-    <row r="298" spans="1:19" ht="11" customHeight="1">
+    <row r="298" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A298" s="4" t="s">
         <v>113</v>
       </c>
@@ -18730,7 +18733,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="299" spans="1:19" ht="11" customHeight="1">
+    <row r="299" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A299" s="4" t="s">
         <v>113</v>
       </c>
@@ -18787,7 +18790,7 @@
       </c>
       <c r="S299" s="6"/>
     </row>
-    <row r="300" spans="1:19" ht="11" customHeight="1">
+    <row r="300" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A300" s="4" t="s">
         <v>113</v>
       </c>
@@ -18844,7 +18847,7 @@
       </c>
       <c r="S300" s="6"/>
     </row>
-    <row r="301" spans="1:19" ht="11" customHeight="1">
+    <row r="301" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A301" s="4" t="s">
         <v>113</v>
       </c>
@@ -18901,7 +18904,7 @@
       </c>
       <c r="S301" s="6"/>
     </row>
-    <row r="302" spans="1:19" ht="11" customHeight="1">
+    <row r="302" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A302" s="4" t="s">
         <v>113</v>
       </c>
@@ -18958,7 +18961,7 @@
       </c>
       <c r="S302" s="6"/>
     </row>
-    <row r="303" spans="1:19" ht="11" customHeight="1">
+    <row r="303" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A303" s="4" t="s">
         <v>113</v>
       </c>
@@ -19017,7 +19020,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="304" spans="1:19" ht="11" customHeight="1">
+    <row r="304" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A304" s="4" t="s">
         <v>113</v>
       </c>
@@ -19074,7 +19077,7 @@
       </c>
       <c r="S304" s="6"/>
     </row>
-    <row r="305" spans="1:19" ht="11" customHeight="1">
+    <row r="305" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A305" s="4" t="s">
         <v>113</v>
       </c>
@@ -19133,7 +19136,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="306" spans="1:19" ht="11" customHeight="1">
+    <row r="306" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A306" s="4" t="s">
         <v>113</v>
       </c>
@@ -19190,7 +19193,7 @@
       </c>
       <c r="S306" s="6"/>
     </row>
-    <row r="307" spans="1:19" ht="11" customHeight="1">
+    <row r="307" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A307" s="4" t="s">
         <v>113</v>
       </c>
@@ -19247,7 +19250,7 @@
       </c>
       <c r="S307" s="6"/>
     </row>
-    <row r="308" spans="1:19" ht="11" customHeight="1">
+    <row r="308" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A308" s="4" t="s">
         <v>113</v>
       </c>
@@ -19304,7 +19307,7 @@
       </c>
       <c r="S308" s="6"/>
     </row>
-    <row r="309" spans="1:19" ht="11" customHeight="1">
+    <row r="309" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A309" s="4" t="s">
         <v>113</v>
       </c>
@@ -19363,7 +19366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="310" spans="1:19" ht="11" customHeight="1">
+    <row r="310" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A310" s="4" t="s">
         <v>113</v>
       </c>
@@ -19422,7 +19425,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="311" spans="1:19" ht="11" customHeight="1">
+    <row r="311" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A311" s="4" t="s">
         <v>113</v>
       </c>
@@ -19479,7 +19482,7 @@
       </c>
       <c r="S311" s="6"/>
     </row>
-    <row r="312" spans="1:19" ht="11" customHeight="1">
+    <row r="312" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A312" s="4" t="s">
         <v>113</v>
       </c>
@@ -19536,7 +19539,7 @@
       </c>
       <c r="S312" s="6"/>
     </row>
-    <row r="313" spans="1:19" ht="11" customHeight="1">
+    <row r="313" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A313" s="4" t="s">
         <v>113</v>
       </c>
@@ -19593,7 +19596,7 @@
       </c>
       <c r="S313" s="6"/>
     </row>
-    <row r="314" spans="1:19" ht="11" customHeight="1">
+    <row r="314" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A314" s="4" t="s">
         <v>113</v>
       </c>
@@ -19650,7 +19653,7 @@
       </c>
       <c r="S314" s="6"/>
     </row>
-    <row r="315" spans="1:19" ht="11" customHeight="1">
+    <row r="315" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A315" s="4" t="s">
         <v>113</v>
       </c>
@@ -19709,7 +19712,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="316" spans="1:19" ht="11" customHeight="1">
+    <row r="316" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A316" s="4" t="s">
         <v>113</v>
       </c>
@@ -19766,7 +19769,7 @@
       </c>
       <c r="S316" s="6"/>
     </row>
-    <row r="317" spans="1:19" ht="11" customHeight="1">
+    <row r="317" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A317" s="4" t="s">
         <v>113</v>
       </c>
@@ -19823,7 +19826,7 @@
       </c>
       <c r="S317" s="6"/>
     </row>
-    <row r="318" spans="1:19" ht="11" customHeight="1">
+    <row r="318" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A318" s="4" t="s">
         <v>113</v>
       </c>
@@ -19880,7 +19883,7 @@
       </c>
       <c r="S318" s="6"/>
     </row>
-    <row r="319" spans="1:19" ht="11" customHeight="1">
+    <row r="319" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A319" s="4" t="s">
         <v>113</v>
       </c>
@@ -19937,7 +19940,7 @@
       </c>
       <c r="S319" s="6"/>
     </row>
-    <row r="320" spans="1:19" ht="11" customHeight="1">
+    <row r="320" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A320" s="4" t="s">
         <v>113</v>
       </c>
@@ -19996,7 +19999,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="321" spans="1:19" ht="11" customHeight="1">
+    <row r="321" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A321" s="4" t="s">
         <v>113</v>
       </c>
@@ -20046,7 +20049,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="322" spans="1:19" ht="11" customHeight="1">
+    <row r="322" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A322" s="4" t="s">
         <v>113</v>
       </c>
@@ -20103,7 +20106,7 @@
       </c>
       <c r="S322" s="6"/>
     </row>
-    <row r="323" spans="1:19" ht="11" customHeight="1">
+    <row r="323" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A323" s="4" t="s">
         <v>113</v>
       </c>
@@ -20160,7 +20163,7 @@
       </c>
       <c r="S323" s="6"/>
     </row>
-    <row r="324" spans="1:19" ht="11" customHeight="1">
+    <row r="324" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A324" s="4" t="s">
         <v>113</v>
       </c>
@@ -20217,7 +20220,7 @@
       </c>
       <c r="S324" s="6"/>
     </row>
-    <row r="325" spans="1:19" ht="11" customHeight="1">
+    <row r="325" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A325" s="4" t="s">
         <v>113</v>
       </c>
@@ -20274,7 +20277,7 @@
       </c>
       <c r="S325" s="6"/>
     </row>
-    <row r="326" spans="1:19" ht="11" customHeight="1">
+    <row r="326" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A326" s="4" t="s">
         <v>113</v>
       </c>
@@ -20331,7 +20334,7 @@
       </c>
       <c r="S326" s="6"/>
     </row>
-    <row r="327" spans="1:19" ht="11" customHeight="1">
+    <row r="327" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A327" s="4" t="s">
         <v>113</v>
       </c>
@@ -20388,7 +20391,7 @@
       </c>
       <c r="S327" s="6"/>
     </row>
-    <row r="328" spans="1:19" ht="11" customHeight="1">
+    <row r="328" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A328" s="4" t="s">
         <v>113</v>
       </c>
@@ -20445,7 +20448,7 @@
       </c>
       <c r="S328" s="6"/>
     </row>
-    <row r="329" spans="1:19" ht="11" customHeight="1">
+    <row r="329" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A329" s="4" t="s">
         <v>113</v>
       </c>
@@ -20502,7 +20505,7 @@
       </c>
       <c r="S329" s="6"/>
     </row>
-    <row r="330" spans="1:19" ht="11" customHeight="1">
+    <row r="330" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A330" s="4" t="s">
         <v>113</v>
       </c>
@@ -20559,7 +20562,7 @@
       </c>
       <c r="S330" s="6"/>
     </row>
-    <row r="331" spans="1:19" ht="11" customHeight="1">
+    <row r="331" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A331" s="4" t="s">
         <v>113</v>
       </c>
@@ -20618,7 +20621,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="332" spans="1:19" ht="11" customHeight="1">
+    <row r="332" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A332" s="4" t="s">
         <v>113</v>
       </c>
@@ -20675,7 +20678,7 @@
       </c>
       <c r="S332" s="6"/>
     </row>
-    <row r="333" spans="1:19" ht="11" customHeight="1">
+    <row r="333" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A333" s="4" t="s">
         <v>113</v>
       </c>
@@ -20725,7 +20728,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="334" spans="1:19" ht="11" customHeight="1">
+    <row r="334" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A334" s="4" t="s">
         <v>113</v>
       </c>
@@ -20775,7 +20778,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="335" spans="1:19" ht="11" customHeight="1">
+    <row r="335" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A335" s="4" t="s">
         <v>113</v>
       </c>
@@ -20834,7 +20837,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="336" spans="1:19" ht="11" customHeight="1">
+    <row r="336" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A336" s="4" t="s">
         <v>113</v>
       </c>
@@ -20891,7 +20894,7 @@
       </c>
       <c r="S336" s="6"/>
     </row>
-    <row r="337" spans="1:19" ht="11" customHeight="1">
+    <row r="337" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A337" s="4" t="s">
         <v>113</v>
       </c>
@@ -20950,7 +20953,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="338" spans="1:19" ht="11" customHeight="1">
+    <row r="338" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A338" s="4" t="s">
         <v>113</v>
       </c>
@@ -21007,7 +21010,7 @@
       </c>
       <c r="S338" s="6"/>
     </row>
-    <row r="339" spans="1:19" ht="11" customHeight="1">
+    <row r="339" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A339" s="4" t="s">
         <v>113</v>
       </c>
@@ -21066,7 +21069,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="340" spans="1:19" ht="11" customHeight="1">
+    <row r="340" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A340" s="4" t="s">
         <v>113</v>
       </c>
@@ -21123,7 +21126,7 @@
       </c>
       <c r="S340" s="6"/>
     </row>
-    <row r="341" spans="1:19" ht="11" customHeight="1">
+    <row r="341" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A341" s="4" t="s">
         <v>113</v>
       </c>
@@ -21182,7 +21185,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="342" spans="1:19" ht="11" customHeight="1">
+    <row r="342" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A342" s="4" t="s">
         <v>113</v>
       </c>
@@ -21239,7 +21242,7 @@
       </c>
       <c r="S342" s="6"/>
     </row>
-    <row r="343" spans="1:19" ht="11" customHeight="1">
+    <row r="343" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A343" s="4" t="s">
         <v>113</v>
       </c>
@@ -21289,7 +21292,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="344" spans="1:19" ht="11" customHeight="1">
+    <row r="344" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A344" s="4" t="s">
         <v>113</v>
       </c>
@@ -21348,7 +21351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:19" ht="11" customHeight="1">
+    <row r="345" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A345" s="4" t="s">
         <v>113</v>
       </c>
@@ -21405,7 +21408,7 @@
       </c>
       <c r="S345" s="6"/>
     </row>
-    <row r="346" spans="1:19" ht="11" customHeight="1">
+    <row r="346" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A346" s="4" t="s">
         <v>113</v>
       </c>
@@ -21462,7 +21465,7 @@
       </c>
       <c r="S346" s="6"/>
     </row>
-    <row r="347" spans="1:19" ht="11" customHeight="1">
+    <row r="347" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A347" s="4" t="s">
         <v>113</v>
       </c>
@@ -21521,7 +21524,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="348" spans="1:19" ht="11" customHeight="1">
+    <row r="348" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A348" s="4" t="s">
         <v>113</v>
       </c>
@@ -21571,7 +21574,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="349" spans="1:19" ht="11" customHeight="1">
+    <row r="349" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A349" s="4" t="s">
         <v>113</v>
       </c>
@@ -21628,7 +21631,7 @@
       </c>
       <c r="S349" s="6"/>
     </row>
-    <row r="350" spans="1:19" ht="11" customHeight="1">
+    <row r="350" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A350" s="4" t="s">
         <v>113</v>
       </c>
@@ -21687,7 +21690,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="351" spans="1:19" ht="11" customHeight="1">
+    <row r="351" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A351" s="4" t="s">
         <v>113</v>
       </c>
@@ -21744,7 +21747,7 @@
       </c>
       <c r="S351" s="6"/>
     </row>
-    <row r="352" spans="1:19" ht="11" customHeight="1">
+    <row r="352" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A352" s="4" t="s">
         <v>113</v>
       </c>
@@ -21801,7 +21804,7 @@
       </c>
       <c r="S352" s="6"/>
     </row>
-    <row r="353" spans="1:19" ht="11" customHeight="1">
+    <row r="353" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A353" s="4" t="s">
         <v>113</v>
       </c>
@@ -21858,7 +21861,7 @@
       </c>
       <c r="S353" s="6"/>
     </row>
-    <row r="354" spans="1:19" ht="11" customHeight="1">
+    <row r="354" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A354" s="4" t="s">
         <v>113</v>
       </c>
@@ -21917,7 +21920,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="355" spans="1:19" ht="11" customHeight="1">
+    <row r="355" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A355" s="4" t="s">
         <v>113</v>
       </c>
@@ -21974,7 +21977,7 @@
       </c>
       <c r="S355" s="6"/>
     </row>
-    <row r="356" spans="1:19" ht="11" customHeight="1">
+    <row r="356" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A356" s="4" t="s">
         <v>113</v>
       </c>
@@ -22031,7 +22034,7 @@
       </c>
       <c r="S356" s="6"/>
     </row>
-    <row r="357" spans="1:19" ht="11" customHeight="1">
+    <row r="357" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A357" s="4" t="s">
         <v>113</v>
       </c>
@@ -22088,7 +22091,7 @@
       </c>
       <c r="S357" s="6"/>
     </row>
-    <row r="358" spans="1:19" ht="11" customHeight="1">
+    <row r="358" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A358" s="4" t="s">
         <v>113</v>
       </c>
@@ -22138,7 +22141,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="359" spans="1:19" ht="11" customHeight="1">
+    <row r="359" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A359" s="4" t="s">
         <v>113</v>
       </c>
@@ -22195,7 +22198,7 @@
       </c>
       <c r="S359" s="6"/>
     </row>
-    <row r="360" spans="1:19" ht="11" customHeight="1">
+    <row r="360" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A360" s="4" t="s">
         <v>113</v>
       </c>
@@ -22252,7 +22255,7 @@
       </c>
       <c r="S360" s="6"/>
     </row>
-    <row r="361" spans="1:19" ht="11" customHeight="1">
+    <row r="361" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A361" s="4" t="s">
         <v>113</v>
       </c>
@@ -22309,7 +22312,7 @@
       </c>
       <c r="S361" s="6"/>
     </row>
-    <row r="362" spans="1:19" ht="11" customHeight="1">
+    <row r="362" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A362" s="4" t="s">
         <v>113</v>
       </c>
@@ -22366,7 +22369,7 @@
       </c>
       <c r="S362" s="6"/>
     </row>
-    <row r="363" spans="1:19" ht="11" customHeight="1">
+    <row r="363" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A363" s="4" t="s">
         <v>113</v>
       </c>
@@ -22423,7 +22426,7 @@
       </c>
       <c r="S363" s="6"/>
     </row>
-    <row r="364" spans="1:19" ht="11" customHeight="1">
+    <row r="364" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A364" s="4" t="s">
         <v>113</v>
       </c>
@@ -22482,7 +22485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:19" ht="11" customHeight="1">
+    <row r="365" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A365" s="4" t="s">
         <v>113</v>
       </c>
@@ -22532,7 +22535,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="366" spans="1:19" ht="11" customHeight="1">
+    <row r="366" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A366" s="4" t="s">
         <v>113</v>
       </c>
@@ -22589,7 +22592,7 @@
       </c>
       <c r="S366" s="10"/>
     </row>
-    <row r="367" spans="1:19" ht="11" customHeight="1">
+    <row r="367" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A367" s="4" t="s">
         <v>113</v>
       </c>
@@ -22648,7 +22651,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="368" spans="1:19" ht="11" customHeight="1">
+    <row r="368" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A368" s="4" t="s">
         <v>113</v>
       </c>
@@ -22705,7 +22708,7 @@
       </c>
       <c r="S368" s="6"/>
     </row>
-    <row r="369" spans="1:19" ht="11" customHeight="1">
+    <row r="369" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A369" s="4" t="s">
         <v>113</v>
       </c>
@@ -22755,7 +22758,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="370" spans="1:19" ht="11" customHeight="1">
+    <row r="370" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A370" s="4" t="s">
         <v>113</v>
       </c>
@@ -22812,7 +22815,7 @@
       </c>
       <c r="S370" s="6"/>
     </row>
-    <row r="371" spans="1:19" ht="11" customHeight="1">
+    <row r="371" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A371" s="4" t="s">
         <v>113</v>
       </c>
@@ -22871,7 +22874,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="372" spans="1:19" ht="11" customHeight="1">
+    <row r="372" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A372" s="4" t="s">
         <v>113</v>
       </c>
@@ -22921,7 +22924,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="373" spans="1:19" ht="11" customHeight="1">
+    <row r="373" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A373" s="4" t="s">
         <v>113</v>
       </c>
@@ -22980,7 +22983,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="374" spans="1:19" ht="11" customHeight="1">
+    <row r="374" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A374" s="4" t="s">
         <v>113</v>
       </c>
@@ -23037,7 +23040,7 @@
       </c>
       <c r="S374" s="6"/>
     </row>
-    <row r="375" spans="1:19" ht="11" customHeight="1">
+    <row r="375" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A375" s="4" t="s">
         <v>113</v>
       </c>
@@ -23094,7 +23097,7 @@
       </c>
       <c r="S375" s="6"/>
     </row>
-    <row r="376" spans="1:19" ht="11" customHeight="1">
+    <row r="376" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A376" s="4" t="s">
         <v>113</v>
       </c>
@@ -23151,7 +23154,7 @@
       </c>
       <c r="S376" s="6"/>
     </row>
-    <row r="377" spans="1:19" ht="11" customHeight="1">
+    <row r="377" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A377" s="4" t="s">
         <v>113</v>
       </c>
@@ -23208,7 +23211,7 @@
       </c>
       <c r="S377" s="6"/>
     </row>
-    <row r="378" spans="1:19" ht="11" customHeight="1">
+    <row r="378" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A378" s="4" t="s">
         <v>113</v>
       </c>
@@ -23265,7 +23268,7 @@
       </c>
       <c r="S378" s="6"/>
     </row>
-    <row r="379" spans="1:19" ht="11" customHeight="1">
+    <row r="379" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A379" s="4" t="s">
         <v>113</v>
       </c>
@@ -23315,7 +23318,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="380" spans="1:19" ht="11" customHeight="1">
+    <row r="380" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A380" s="4" t="s">
         <v>113</v>
       </c>
@@ -23374,7 +23377,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="381" spans="1:19" ht="11" customHeight="1">
+    <row r="381" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A381" s="4" t="s">
         <v>113</v>
       </c>
@@ -23433,7 +23436,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="382" spans="1:19" ht="11" customHeight="1">
+    <row r="382" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A382" s="4" t="s">
         <v>113</v>
       </c>
@@ -23490,7 +23493,7 @@
       </c>
       <c r="S382" s="6"/>
     </row>
-    <row r="383" spans="1:19" ht="11" customHeight="1">
+    <row r="383" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A383" s="4" t="s">
         <v>113</v>
       </c>
@@ -23549,7 +23552,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="384" spans="1:19" ht="11" customHeight="1">
+    <row r="384" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A384" s="4" t="s">
         <v>113</v>
       </c>
@@ -23606,7 +23609,7 @@
       </c>
       <c r="S384" s="6"/>
     </row>
-    <row r="385" spans="1:19" ht="11" customHeight="1">
+    <row r="385" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A385" s="4" t="s">
         <v>113</v>
       </c>
@@ -23663,7 +23666,7 @@
       </c>
       <c r="S385" s="6"/>
     </row>
-    <row r="386" spans="1:19" ht="11" customHeight="1">
+    <row r="386" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A386" s="4" t="s">
         <v>113</v>
       </c>
@@ -23720,7 +23723,7 @@
       </c>
       <c r="S386" s="6"/>
     </row>
-    <row r="387" spans="1:19" ht="11" customHeight="1">
+    <row r="387" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A387" s="4" t="s">
         <v>113</v>
       </c>
@@ -23777,7 +23780,7 @@
       </c>
       <c r="S387" s="6"/>
     </row>
-    <row r="388" spans="1:19" ht="11" customHeight="1">
+    <row r="388" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A388" s="4" t="s">
         <v>113</v>
       </c>
@@ -23836,7 +23839,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="389" spans="1:19" ht="11" customHeight="1">
+    <row r="389" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A389" s="4" t="s">
         <v>113</v>
       </c>
@@ -23893,7 +23896,7 @@
       </c>
       <c r="S389" s="6"/>
     </row>
-    <row r="390" spans="1:19" ht="11" customHeight="1">
+    <row r="390" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A390" s="4" t="s">
         <v>113</v>
       </c>
@@ -23950,7 +23953,7 @@
       </c>
       <c r="S390" s="6"/>
     </row>
-    <row r="391" spans="1:19" ht="11" customHeight="1">
+    <row r="391" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A391" s="4" t="s">
         <v>113</v>
       </c>
@@ -24009,7 +24012,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="392" spans="1:19" ht="11" customHeight="1">
+    <row r="392" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A392" s="4" t="s">
         <v>113</v>
       </c>
@@ -24066,7 +24069,7 @@
       </c>
       <c r="S392" s="6"/>
     </row>
-    <row r="393" spans="1:19" ht="11" customHeight="1">
+    <row r="393" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A393" s="4" t="s">
         <v>113</v>
       </c>
@@ -24123,7 +24126,7 @@
       </c>
       <c r="S393" s="6"/>
     </row>
-    <row r="394" spans="1:19" ht="11" customHeight="1">
+    <row r="394" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A394" s="4" t="s">
         <v>113</v>
       </c>
@@ -24180,7 +24183,7 @@
       </c>
       <c r="S394" s="6"/>
     </row>
-    <row r="395" spans="1:19" ht="11" customHeight="1">
+    <row r="395" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A395" s="4" t="s">
         <v>113</v>
       </c>
@@ -24237,7 +24240,7 @@
       </c>
       <c r="S395" s="6"/>
     </row>
-    <row r="396" spans="1:19" ht="11" customHeight="1">
+    <row r="396" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A396" s="4" t="s">
         <v>113</v>
       </c>
@@ -24287,7 +24290,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="397" spans="1:19" ht="11" customHeight="1">
+    <row r="397" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A397" s="4" t="s">
         <v>113</v>
       </c>
@@ -24344,7 +24347,7 @@
       </c>
       <c r="S397" s="6"/>
     </row>
-    <row r="398" spans="1:19" ht="11" customHeight="1">
+    <row r="398" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A398" s="4" t="s">
         <v>113</v>
       </c>
@@ -24401,7 +24404,7 @@
       </c>
       <c r="S398" s="6"/>
     </row>
-    <row r="399" spans="1:19" ht="11" customHeight="1">
+    <row r="399" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A399" s="4" t="s">
         <v>113</v>
       </c>
@@ -24451,7 +24454,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="400" spans="1:19" ht="11" customHeight="1">
+    <row r="400" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A400" s="4" t="s">
         <v>113</v>
       </c>
@@ -24510,7 +24513,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="401" spans="1:19" ht="11" customHeight="1">
+    <row r="401" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A401" s="4" t="s">
         <v>113</v>
       </c>
@@ -24567,7 +24570,7 @@
       </c>
       <c r="S401" s="6"/>
     </row>
-    <row r="402" spans="1:19" ht="11" customHeight="1">
+    <row r="402" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A402" s="4" t="s">
         <v>113</v>
       </c>
@@ -24624,7 +24627,7 @@
       </c>
       <c r="S402" s="6"/>
     </row>
-    <row r="403" spans="1:19" ht="11" customHeight="1">
+    <row r="403" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A403" s="4" t="s">
         <v>113</v>
       </c>
@@ -24681,7 +24684,7 @@
       </c>
       <c r="S403" s="6"/>
     </row>
-    <row r="404" spans="1:19" ht="11" customHeight="1">
+    <row r="404" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A404" s="4" t="s">
         <v>113</v>
       </c>
@@ -24738,7 +24741,7 @@
       </c>
       <c r="S404" s="6"/>
     </row>
-    <row r="405" spans="1:19" ht="11" customHeight="1">
+    <row r="405" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A405" s="4" t="s">
         <v>113</v>
       </c>
@@ -24795,7 +24798,7 @@
       </c>
       <c r="S405" s="6"/>
     </row>
-    <row r="406" spans="1:19" ht="11" customHeight="1">
+    <row r="406" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A406" s="4" t="s">
         <v>113</v>
       </c>
@@ -24852,7 +24855,7 @@
       </c>
       <c r="S406" s="6"/>
     </row>
-    <row r="407" spans="1:19" ht="11" customHeight="1">
+    <row r="407" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A407" s="4" t="s">
         <v>113</v>
       </c>
@@ -24909,7 +24912,7 @@
       </c>
       <c r="S407" s="6"/>
     </row>
-    <row r="408" spans="1:19" ht="11" customHeight="1">
+    <row r="408" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A408" s="4" t="s">
         <v>113</v>
       </c>
@@ -24966,7 +24969,7 @@
       </c>
       <c r="S408" s="6"/>
     </row>
-    <row r="409" spans="1:19" ht="11" customHeight="1">
+    <row r="409" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A409" s="4" t="s">
         <v>113</v>
       </c>
@@ -25025,7 +25028,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="410" spans="1:19" ht="11" customHeight="1">
+    <row r="410" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A410" s="4" t="s">
         <v>113</v>
       </c>
@@ -25082,7 +25085,7 @@
       </c>
       <c r="S410" s="6"/>
     </row>
-    <row r="411" spans="1:19" ht="11" customHeight="1">
+    <row r="411" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A411" s="4" t="s">
         <v>113</v>
       </c>
@@ -25132,7 +25135,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="412" spans="1:19" ht="11" customHeight="1">
+    <row r="412" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A412" s="4" t="s">
         <v>113</v>
       </c>
@@ -25191,7 +25194,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="413" spans="1:19" ht="11" customHeight="1">
+    <row r="413" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A413" s="4" t="s">
         <v>113</v>
       </c>
@@ -25250,7 +25253,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="414" spans="1:19" ht="11" customHeight="1">
+    <row r="414" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A414" s="4" t="s">
         <v>113</v>
       </c>
@@ -25307,7 +25310,7 @@
       </c>
       <c r="S414" s="6"/>
     </row>
-    <row r="415" spans="1:19" ht="11" customHeight="1">
+    <row r="415" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A415" s="4" t="s">
         <v>113</v>
       </c>
@@ -25357,7 +25360,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="416" spans="1:19" ht="11" customHeight="1">
+    <row r="416" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A416" s="4" t="s">
         <v>113</v>
       </c>
@@ -25407,7 +25410,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="417" spans="1:19" ht="11" customHeight="1">
+    <row r="417" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A417" s="4" t="s">
         <v>113</v>
       </c>
@@ -25464,7 +25467,7 @@
       </c>
       <c r="S417" s="6"/>
     </row>
-    <row r="418" spans="1:19" ht="11" customHeight="1">
+    <row r="418" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A418" s="4" t="s">
         <v>113</v>
       </c>
@@ -25521,7 +25524,7 @@
       </c>
       <c r="S418" s="6"/>
     </row>
-    <row r="419" spans="1:19" ht="11" customHeight="1">
+    <row r="419" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A419" s="4" t="s">
         <v>113</v>
       </c>
@@ -25578,7 +25581,7 @@
       </c>
       <c r="S419" s="6"/>
     </row>
-    <row r="420" spans="1:19" ht="11" customHeight="1">
+    <row r="420" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A420" s="4" t="s">
         <v>113</v>
       </c>
@@ -25628,7 +25631,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="421" spans="1:19" ht="11" customHeight="1">
+    <row r="421" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A421" s="4" t="s">
         <v>113</v>
       </c>
@@ -25687,7 +25690,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="422" spans="1:19" ht="11" customHeight="1">
+    <row r="422" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A422" s="4" t="s">
         <v>113</v>
       </c>
@@ -25737,7 +25740,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="423" spans="1:19" ht="11" customHeight="1">
+    <row r="423" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A423" s="4" t="s">
         <v>113</v>
       </c>
@@ -25794,7 +25797,7 @@
       </c>
       <c r="S423" s="6"/>
     </row>
-    <row r="424" spans="1:19" ht="11" customHeight="1">
+    <row r="424" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A424" s="4" t="s">
         <v>113</v>
       </c>
@@ -25851,7 +25854,7 @@
       </c>
       <c r="S424" s="6"/>
     </row>
-    <row r="425" spans="1:19" ht="11" customHeight="1">
+    <row r="425" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A425" s="4" t="s">
         <v>113</v>
       </c>
@@ -25908,7 +25911,7 @@
       </c>
       <c r="S425" s="6"/>
     </row>
-    <row r="426" spans="1:19" ht="11" customHeight="1">
+    <row r="426" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A426" s="4" t="s">
         <v>113</v>
       </c>
@@ -25965,7 +25968,7 @@
       </c>
       <c r="S426" s="6"/>
     </row>
-    <row r="427" spans="1:19" ht="11" customHeight="1">
+    <row r="427" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A427" s="4" t="s">
         <v>113</v>
       </c>
@@ -26022,7 +26025,7 @@
       </c>
       <c r="S427" s="6"/>
     </row>
-    <row r="428" spans="1:19" ht="11" customHeight="1">
+    <row r="428" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A428" s="4" t="s">
         <v>113</v>
       </c>
@@ -26079,7 +26082,7 @@
       </c>
       <c r="S428" s="6"/>
     </row>
-    <row r="429" spans="1:19" ht="11" customHeight="1">
+    <row r="429" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A429" s="4" t="s">
         <v>113</v>
       </c>
@@ -26136,7 +26139,7 @@
       </c>
       <c r="S429" s="6"/>
     </row>
-    <row r="430" spans="1:19" ht="11" customHeight="1">
+    <row r="430" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A430" s="4" t="s">
         <v>113</v>
       </c>
@@ -26186,7 +26189,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="431" spans="1:19" ht="11" customHeight="1">
+    <row r="431" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A431" s="4" t="s">
         <v>113</v>
       </c>
@@ -26243,7 +26246,7 @@
       </c>
       <c r="S431" s="6"/>
     </row>
-    <row r="432" spans="1:19" ht="11" customHeight="1">
+    <row r="432" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A432" s="4" t="s">
         <v>113</v>
       </c>
@@ -26300,7 +26303,7 @@
       </c>
       <c r="S432" s="6"/>
     </row>
-    <row r="433" spans="1:19" ht="11" customHeight="1">
+    <row r="433" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A433" s="4" t="s">
         <v>113</v>
       </c>
@@ -26357,7 +26360,7 @@
       </c>
       <c r="S433" s="6"/>
     </row>
-    <row r="434" spans="1:19" ht="11" customHeight="1">
+    <row r="434" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A434" s="4" t="s">
         <v>113</v>
       </c>
@@ -26416,7 +26419,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="435" spans="1:19" ht="11" customHeight="1">
+    <row r="435" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A435" s="4" t="s">
         <v>113</v>
       </c>
@@ -26473,7 +26476,7 @@
       </c>
       <c r="S435" s="6"/>
     </row>
-    <row r="436" spans="1:19" ht="11" customHeight="1">
+    <row r="436" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A436" s="4" t="s">
         <v>113</v>
       </c>
@@ -26530,7 +26533,7 @@
       </c>
       <c r="S436" s="6"/>
     </row>
-    <row r="437" spans="1:19" ht="11" customHeight="1">
+    <row r="437" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A437" s="4" t="s">
         <v>133</v>
       </c>
@@ -26589,7 +26592,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="438" spans="1:19" ht="11" customHeight="1">
+    <row r="438" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A438" s="4" t="s">
         <v>133</v>
       </c>
@@ -26648,7 +26651,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="439" spans="1:19" ht="11" customHeight="1">
+    <row r="439" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A439" s="4" t="s">
         <v>133</v>
       </c>
@@ -26707,7 +26710,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="440" spans="1:19" ht="11" customHeight="1">
+    <row r="440" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A440" s="4" t="s">
         <v>133</v>
       </c>
@@ -26766,7 +26769,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="441" spans="1:19" ht="11" customHeight="1">
+    <row r="441" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A441" s="4" t="s">
         <v>133</v>
       </c>
@@ -26823,7 +26826,7 @@
       </c>
       <c r="S441" s="6"/>
     </row>
-    <row r="442" spans="1:19" ht="11" customHeight="1">
+    <row r="442" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A442" s="4" t="s">
         <v>133</v>
       </c>
@@ -26925,8 +26928,8 @@
       <c r="N443" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="O443" s="4">
-        <v>0</v>
+      <c r="O443" s="4" t="s">
+        <v>83</v>
       </c>
       <c r="P443" s="5" t="s">
         <v>142</v>
@@ -26941,7 +26944,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="444" spans="1:19" ht="11" customHeight="1">
+    <row r="444" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A444" s="4" t="s">
         <v>133</v>
       </c>
@@ -26998,7 +27001,7 @@
       </c>
       <c r="S444" s="6"/>
     </row>
-    <row r="445" spans="1:19" ht="11" customHeight="1">
+    <row r="445" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A445" s="4" t="s">
         <v>133</v>
       </c>
@@ -27055,7 +27058,7 @@
       </c>
       <c r="S445" s="6"/>
     </row>
-    <row r="446" spans="1:19" ht="11" customHeight="1">
+    <row r="446" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A446" s="4" t="s">
         <v>133</v>
       </c>
@@ -27112,7 +27115,7 @@
       </c>
       <c r="S446" s="6"/>
     </row>
-    <row r="447" spans="1:19" ht="11" customHeight="1">
+    <row r="447" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A447" s="4" t="s">
         <v>133</v>
       </c>
@@ -27169,7 +27172,7 @@
       </c>
       <c r="S447" s="6"/>
     </row>
-    <row r="448" spans="1:19" ht="11" customHeight="1">
+    <row r="448" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A448" s="4" t="s">
         <v>133</v>
       </c>
@@ -27228,7 +27231,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="449" spans="1:19" ht="11" customHeight="1">
+    <row r="449" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A449" s="4" t="s">
         <v>133</v>
       </c>
@@ -27285,7 +27288,7 @@
       </c>
       <c r="S449" s="6"/>
     </row>
-    <row r="450" spans="1:19" ht="11" customHeight="1">
+    <row r="450" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A450" s="4" t="s">
         <v>133</v>
       </c>
@@ -27344,7 +27347,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="451" spans="1:19" ht="11" customHeight="1">
+    <row r="451" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A451" s="4" t="s">
         <v>133</v>
       </c>
@@ -27403,7 +27406,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="452" spans="1:19" ht="11" customHeight="1">
+    <row r="452" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A452" s="4" t="s">
         <v>133</v>
       </c>
@@ -27453,7 +27456,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="453" spans="1:19" ht="11" customHeight="1">
+    <row r="453" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A453" s="4" t="s">
         <v>133</v>
       </c>
@@ -27510,7 +27513,7 @@
       </c>
       <c r="S453" s="6"/>
     </row>
-    <row r="454" spans="1:19" ht="11" customHeight="1">
+    <row r="454" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A454" s="4" t="s">
         <v>133</v>
       </c>
@@ -27569,7 +27572,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="455" spans="1:19" ht="11" customHeight="1">
+    <row r="455" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A455" s="4" t="s">
         <v>133</v>
       </c>
@@ -27626,7 +27629,7 @@
       </c>
       <c r="S455" s="6"/>
     </row>
-    <row r="456" spans="1:19" ht="11" customHeight="1">
+    <row r="456" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A456" s="4" t="s">
         <v>133</v>
       </c>
@@ -27683,7 +27686,7 @@
       </c>
       <c r="S456" s="6"/>
     </row>
-    <row r="457" spans="1:19" ht="11" customHeight="1">
+    <row r="457" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A457" s="4" t="s">
         <v>133</v>
       </c>
@@ -27745,7 +27748,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="458" spans="1:19" ht="11" customHeight="1">
+    <row r="458" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A458" s="4" t="s">
         <v>133</v>
       </c>
@@ -27804,7 +27807,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="459" spans="1:19" ht="11" customHeight="1">
+    <row r="459" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A459" s="4" t="s">
         <v>133</v>
       </c>
@@ -27863,7 +27866,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="460" spans="1:19" ht="11" customHeight="1">
+    <row r="460" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A460" s="4" t="s">
         <v>133</v>
       </c>
@@ -27922,7 +27925,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="461" spans="1:19" ht="11" customHeight="1">
+    <row r="461" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A461" s="4" t="s">
         <v>133</v>
       </c>
@@ -27979,7 +27982,7 @@
       </c>
       <c r="S461" s="6"/>
     </row>
-    <row r="462" spans="1:19" ht="11" customHeight="1">
+    <row r="462" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A462" s="4" t="s">
         <v>133</v>
       </c>
@@ -28038,7 +28041,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="463" spans="1:19" ht="11" customHeight="1">
+    <row r="463" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A463" s="4" t="s">
         <v>133</v>
       </c>
@@ -28095,7 +28098,7 @@
       </c>
       <c r="S463" s="6"/>
     </row>
-    <row r="464" spans="1:19" ht="11" customHeight="1">
+    <row r="464" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A464" s="4" t="s">
         <v>133</v>
       </c>
@@ -28154,7 +28157,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="465" spans="1:19" ht="11" customHeight="1">
+    <row r="465" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A465" s="4" t="s">
         <v>133</v>
       </c>
@@ -28213,7 +28216,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="466" spans="1:19" ht="11" customHeight="1">
+    <row r="466" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A466" s="4" t="s">
         <v>133</v>
       </c>
@@ -28270,7 +28273,7 @@
       </c>
       <c r="S466" s="6"/>
     </row>
-    <row r="467" spans="1:19" ht="11" customHeight="1">
+    <row r="467" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A467" s="4" t="s">
         <v>133</v>
       </c>
@@ -28327,7 +28330,7 @@
       </c>
       <c r="S467" s="6"/>
     </row>
-    <row r="468" spans="1:19" ht="11" customHeight="1">
+    <row r="468" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A468" s="4" t="s">
         <v>133</v>
       </c>
@@ -28377,7 +28380,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="469" spans="1:19" ht="11" customHeight="1">
+    <row r="469" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A469" s="4" t="s">
         <v>133</v>
       </c>
@@ -28436,7 +28439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:19" ht="11" customHeight="1">
+    <row r="470" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A470" s="4" t="s">
         <v>133</v>
       </c>
@@ -28493,7 +28496,7 @@
       </c>
       <c r="S470" s="6"/>
     </row>
-    <row r="471" spans="1:19" ht="11" customHeight="1">
+    <row r="471" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A471" s="4" t="s">
         <v>133</v>
       </c>
@@ -28550,7 +28553,7 @@
       </c>
       <c r="S471" s="6"/>
     </row>
-    <row r="472" spans="1:19" ht="11" customHeight="1">
+    <row r="472" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A472" s="4" t="s">
         <v>133</v>
       </c>
@@ -28609,7 +28612,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="473" spans="1:19" ht="11" customHeight="1">
+    <row r="473" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A473" s="4" t="s">
         <v>133</v>
       </c>
@@ -28666,7 +28669,7 @@
       </c>
       <c r="S473" s="6"/>
     </row>
-    <row r="474" spans="1:19" ht="11" customHeight="1">
+    <row r="474" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A474" s="4" t="s">
         <v>133</v>
       </c>
@@ -28725,7 +28728,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="475" spans="1:19" ht="11" customHeight="1">
+    <row r="475" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A475" s="4" t="s">
         <v>133</v>
       </c>
@@ -28782,7 +28785,7 @@
       </c>
       <c r="S475" s="6"/>
     </row>
-    <row r="476" spans="1:19" ht="11" customHeight="1">
+    <row r="476" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A476" s="4" t="s">
         <v>133</v>
       </c>
@@ -28832,7 +28835,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="477" spans="1:19" ht="11" customHeight="1">
+    <row r="477" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A477" s="4" t="s">
         <v>133</v>
       </c>
@@ -28891,7 +28894,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="478" spans="1:19" ht="11" customHeight="1">
+    <row r="478" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A478" s="4" t="s">
         <v>133</v>
       </c>
@@ -28950,7 +28953,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="479" spans="1:19" ht="11" customHeight="1">
+    <row r="479" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A479" s="4" t="s">
         <v>133</v>
       </c>
@@ -29007,7 +29010,7 @@
       </c>
       <c r="S479" s="6"/>
     </row>
-    <row r="480" spans="1:19" ht="11" customHeight="1">
+    <row r="480" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A480" s="4" t="s">
         <v>133</v>
       </c>
@@ -29066,7 +29069,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="481" spans="1:19" ht="11" customHeight="1">
+    <row r="481" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A481" s="4" t="s">
         <v>133</v>
       </c>
@@ -29125,7 +29128,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="482" spans="1:19" ht="11" customHeight="1">
+    <row r="482" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A482" s="4" t="s">
         <v>133</v>
       </c>
@@ -29182,7 +29185,7 @@
       </c>
       <c r="S482" s="6"/>
     </row>
-    <row r="483" spans="1:19" ht="11" customHeight="1">
+    <row r="483" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A483" s="4" t="s">
         <v>133</v>
       </c>
@@ -29239,7 +29242,7 @@
       </c>
       <c r="S483" s="6"/>
     </row>
-    <row r="484" spans="1:19" ht="11" customHeight="1">
+    <row r="484" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A484" s="4" t="s">
         <v>133</v>
       </c>
@@ -29298,7 +29301,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="485" spans="1:19" ht="11" customHeight="1">
+    <row r="485" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A485" s="4" t="s">
         <v>133</v>
       </c>
@@ -29357,7 +29360,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="486" spans="1:19" ht="11" customHeight="1">
+    <row r="486" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A486" s="4" t="s">
         <v>133</v>
       </c>
@@ -29416,7 +29419,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="487" spans="1:19" ht="11" customHeight="1">
+    <row r="487" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A487" s="4" t="s">
         <v>133</v>
       </c>
@@ -29475,7 +29478,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="488" spans="1:19" ht="11" customHeight="1">
+    <row r="488" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A488" s="4" t="s">
         <v>133</v>
       </c>
@@ -29532,7 +29535,7 @@
       </c>
       <c r="S488" s="6"/>
     </row>
-    <row r="489" spans="1:19" ht="11" customHeight="1">
+    <row r="489" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A489" s="4" t="s">
         <v>133</v>
       </c>
@@ -29591,7 +29594,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="490" spans="1:19" ht="11" customHeight="1">
+    <row r="490" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A490" s="4" t="s">
         <v>133</v>
       </c>
@@ -29648,7 +29651,7 @@
       </c>
       <c r="S490" s="6"/>
     </row>
-    <row r="491" spans="1:19" ht="11" customHeight="1">
+    <row r="491" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A491" s="4" t="s">
         <v>133</v>
       </c>
@@ -29705,7 +29708,7 @@
       </c>
       <c r="S491" s="6"/>
     </row>
-    <row r="492" spans="1:19" ht="11" customHeight="1">
+    <row r="492" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A492" s="4" t="s">
         <v>133</v>
       </c>
@@ -29764,7 +29767,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="493" spans="1:19" ht="11" customHeight="1">
+    <row r="493" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A493" s="4" t="s">
         <v>133</v>
       </c>
@@ -29814,7 +29817,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="494" spans="1:19" ht="11" customHeight="1">
+    <row r="494" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A494" s="4" t="s">
         <v>133</v>
       </c>
@@ -29864,7 +29867,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="495" spans="1:19" ht="11" customHeight="1">
+    <row r="495" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A495" s="4" t="s">
         <v>133</v>
       </c>
@@ -29921,7 +29924,7 @@
       </c>
       <c r="S495" s="6"/>
     </row>
-    <row r="496" spans="1:19" ht="11" customHeight="1">
+    <row r="496" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A496" s="4" t="s">
         <v>133</v>
       </c>
@@ -29980,7 +29983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="497" spans="1:19" ht="11" customHeight="1">
+    <row r="497" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A497" s="4" t="s">
         <v>133</v>
       </c>
@@ -30037,7 +30040,7 @@
       </c>
       <c r="S497" s="6"/>
     </row>
-    <row r="498" spans="1:19" ht="11" customHeight="1">
+    <row r="498" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A498" s="4" t="s">
         <v>133</v>
       </c>
@@ -30094,7 +30097,7 @@
       </c>
       <c r="S498" s="6"/>
     </row>
-    <row r="499" spans="1:19" ht="11" customHeight="1">
+    <row r="499" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A499" s="4" t="s">
         <v>133</v>
       </c>
@@ -30151,7 +30154,7 @@
       </c>
       <c r="S499" s="6"/>
     </row>
-    <row r="500" spans="1:19" ht="11" customHeight="1">
+    <row r="500" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A500" s="4" t="s">
         <v>133</v>
       </c>
@@ -30210,7 +30213,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="501" spans="1:19" ht="11" customHeight="1">
+    <row r="501" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A501" s="4" t="s">
         <v>133</v>
       </c>
@@ -30267,7 +30270,7 @@
       </c>
       <c r="S501" s="6"/>
     </row>
-    <row r="502" spans="1:19" ht="11" customHeight="1">
+    <row r="502" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A502" s="4" t="s">
         <v>133</v>
       </c>
@@ -30326,7 +30329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:19" ht="11" customHeight="1">
+    <row r="503" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A503" s="4" t="s">
         <v>133</v>
       </c>
@@ -30385,7 +30388,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="504" spans="1:19" ht="11" customHeight="1">
+    <row r="504" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A504" s="4" t="s">
         <v>133</v>
       </c>
@@ -30444,7 +30447,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="505" spans="1:19" ht="11" customHeight="1">
+    <row r="505" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A505" s="4" t="s">
         <v>133</v>
       </c>
@@ -30503,7 +30506,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="506" spans="1:19" ht="11" customHeight="1">
+    <row r="506" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A506" s="4" t="s">
         <v>133</v>
       </c>
@@ -30562,7 +30565,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:19" ht="11" customHeight="1">
+    <row r="507" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A507" s="4" t="s">
         <v>133</v>
       </c>
@@ -30612,7 +30615,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="508" spans="1:19" ht="11" customHeight="1">
+    <row r="508" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A508" s="4" t="s">
         <v>133</v>
       </c>
@@ -30662,7 +30665,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="509" spans="1:19" ht="11" customHeight="1">
+    <row r="509" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A509" s="4" t="s">
         <v>133</v>
       </c>
@@ -30712,7 +30715,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="510" spans="1:19" ht="11" customHeight="1">
+    <row r="510" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A510" s="4" t="s">
         <v>133</v>
       </c>
@@ -30771,7 +30774,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="511" spans="1:19" ht="11" customHeight="1">
+    <row r="511" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A511" s="4" t="s">
         <v>133</v>
       </c>
@@ -30828,7 +30831,7 @@
       </c>
       <c r="S511" s="6"/>
     </row>
-    <row r="512" spans="1:19" ht="11" customHeight="1">
+    <row r="512" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A512" s="4" t="s">
         <v>133</v>
       </c>
@@ -30887,7 +30890,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="513" spans="1:19" ht="11" customHeight="1">
+    <row r="513" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A513" s="4" t="s">
         <v>133</v>
       </c>
@@ -30946,7 +30949,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="514" spans="1:19" ht="11" customHeight="1">
+    <row r="514" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A514" s="4" t="s">
         <v>133</v>
       </c>
@@ -31005,7 +31008,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="515" spans="1:19" ht="11" customHeight="1">
+    <row r="515" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A515" s="4" t="s">
         <v>133</v>
       </c>
@@ -31062,7 +31065,7 @@
       </c>
       <c r="S515" s="6"/>
     </row>
-    <row r="516" spans="1:19" ht="11" customHeight="1">
+    <row r="516" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A516" s="4" t="s">
         <v>133</v>
       </c>
@@ -31124,7 +31127,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="517" spans="1:19" ht="11" customHeight="1">
+    <row r="517" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A517" s="4" t="s">
         <v>133</v>
       </c>
@@ -31183,7 +31186,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="518" spans="1:19" ht="11" customHeight="1">
+    <row r="518" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A518" s="4" t="s">
         <v>133</v>
       </c>
@@ -31242,7 +31245,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="519" spans="1:19" ht="11" customHeight="1">
+    <row r="519" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A519" s="4" t="s">
         <v>133</v>
       </c>
@@ -31301,7 +31304,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="520" spans="1:19" ht="11" customHeight="1">
+    <row r="520" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A520" s="4" t="s">
         <v>133</v>
       </c>
@@ -31358,7 +31361,7 @@
       </c>
       <c r="S520" s="6"/>
     </row>
-    <row r="521" spans="1:19" ht="11" customHeight="1">
+    <row r="521" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A521" s="4" t="s">
         <v>133</v>
       </c>
@@ -31417,7 +31420,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="522" spans="1:19" ht="11" customHeight="1">
+    <row r="522" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A522" s="4" t="s">
         <v>133</v>
       </c>
@@ -31476,7 +31479,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="523" spans="1:19" ht="11" customHeight="1">
+    <row r="523" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A523" s="4" t="s">
         <v>133</v>
       </c>
@@ -31533,7 +31536,7 @@
       </c>
       <c r="S523" s="6"/>
     </row>
-    <row r="524" spans="1:19" ht="11" customHeight="1">
+    <row r="524" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A524" s="4" t="s">
         <v>133</v>
       </c>
@@ -31592,7 +31595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:19" ht="11" customHeight="1">
+    <row r="525" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A525" s="4" t="s">
         <v>133</v>
       </c>
@@ -31642,7 +31645,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="526" spans="1:19" ht="11" customHeight="1">
+    <row r="526" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A526" s="4" t="s">
         <v>133</v>
       </c>
@@ -31701,7 +31704,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="527" spans="1:19" ht="11" customHeight="1">
+    <row r="527" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A527" s="4" t="s">
         <v>133</v>
       </c>
@@ -31749,7 +31752,7 @@
       </c>
       <c r="S527" s="6"/>
     </row>
-    <row r="528" spans="1:19" ht="11" customHeight="1">
+    <row r="528" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A528" s="4" t="s">
         <v>133</v>
       </c>
@@ -31806,7 +31809,7 @@
       </c>
       <c r="S528" s="6"/>
     </row>
-    <row r="529" spans="1:19" ht="11" customHeight="1">
+    <row r="529" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A529" s="4" t="s">
         <v>133</v>
       </c>
@@ -31863,7 +31866,7 @@
       </c>
       <c r="S529" s="6"/>
     </row>
-    <row r="530" spans="1:19" ht="11" customHeight="1">
+    <row r="530" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A530" s="4" t="s">
         <v>133</v>
       </c>
@@ -31913,7 +31916,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="531" spans="1:19" ht="11" customHeight="1">
+    <row r="531" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A531" s="4" t="s">
         <v>133</v>
       </c>
@@ -31970,7 +31973,7 @@
       </c>
       <c r="S531" s="6"/>
     </row>
-    <row r="532" spans="1:19" ht="11" customHeight="1">
+    <row r="532" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A532" s="4" t="s">
         <v>133</v>
       </c>
@@ -32029,7 +32032,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="533" spans="1:19" ht="11" customHeight="1">
+    <row r="533" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A533" s="4" t="s">
         <v>133</v>
       </c>
@@ -32079,7 +32082,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="534" spans="1:19" ht="11" customHeight="1">
+    <row r="534" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A534" s="4" t="s">
         <v>133</v>
       </c>
@@ -32138,7 +32141,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="535" spans="1:19" ht="11" customHeight="1">
+    <row r="535" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A535" s="4" t="s">
         <v>133</v>
       </c>
@@ -32197,7 +32200,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="536" spans="1:19" ht="11" customHeight="1">
+    <row r="536" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A536" s="4" t="s">
         <v>133</v>
       </c>
@@ -32247,7 +32250,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="537" spans="1:19" ht="11" customHeight="1">
+    <row r="537" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A537" s="4" t="s">
         <v>133</v>
       </c>
@@ -32306,7 +32309,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="538" spans="1:19" ht="11" customHeight="1">
+    <row r="538" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A538" s="4" t="s">
         <v>133</v>
       </c>
@@ -32365,7 +32368,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="539" spans="1:19" ht="11" customHeight="1">
+    <row r="539" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A539" s="4" t="s">
         <v>133</v>
       </c>
@@ -32422,7 +32425,7 @@
       </c>
       <c r="S539" s="6"/>
     </row>
-    <row r="540" spans="1:19" ht="11" customHeight="1">
+    <row r="540" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A540" s="4" t="s">
         <v>133</v>
       </c>
@@ -32472,7 +32475,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="541" spans="1:19" ht="11" customHeight="1">
+    <row r="541" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A541" s="4" t="s">
         <v>133</v>
       </c>
@@ -32531,7 +32534,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="542" spans="1:19" ht="11" customHeight="1">
+    <row r="542" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A542" s="4" t="s">
         <v>133</v>
       </c>
@@ -32588,7 +32591,7 @@
       </c>
       <c r="S542" s="6"/>
     </row>
-    <row r="543" spans="1:19" ht="11" customHeight="1">
+    <row r="543" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A543" s="4" t="s">
         <v>133</v>
       </c>
@@ -32645,7 +32648,7 @@
       </c>
       <c r="S543" s="6"/>
     </row>
-    <row r="544" spans="1:19" ht="11" customHeight="1">
+    <row r="544" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A544" s="4" t="s">
         <v>133</v>
       </c>
@@ -32704,7 +32707,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="545" spans="1:19" ht="11" customHeight="1">
+    <row r="545" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A545" s="4" t="s">
         <v>133</v>
       </c>
@@ -32761,7 +32764,7 @@
       </c>
       <c r="S545" s="6"/>
     </row>
-    <row r="546" spans="1:19" ht="11" customHeight="1">
+    <row r="546" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A546" s="4" t="s">
         <v>133</v>
       </c>
@@ -32818,7 +32821,7 @@
       </c>
       <c r="S546" s="6"/>
     </row>
-    <row r="547" spans="1:19" ht="11" customHeight="1">
+    <row r="547" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A547" s="4" t="s">
         <v>133</v>
       </c>
@@ -32877,7 +32880,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="548" spans="1:19" ht="11" customHeight="1">
+    <row r="548" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A548" s="4" t="s">
         <v>133</v>
       </c>
@@ -32934,7 +32937,7 @@
       </c>
       <c r="S548" s="6"/>
     </row>
-    <row r="549" spans="1:19" ht="11" customHeight="1">
+    <row r="549" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A549" s="4" t="s">
         <v>133</v>
       </c>
@@ -32991,7 +32994,7 @@
       </c>
       <c r="S549" s="6"/>
     </row>
-    <row r="550" spans="1:19" ht="11" customHeight="1">
+    <row r="550" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A550" s="4" t="s">
         <v>173</v>
       </c>
@@ -33050,7 +33053,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="551" spans="1:19" ht="11" customHeight="1">
+    <row r="551" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A551" s="4" t="s">
         <v>173</v>
       </c>
@@ -33100,7 +33103,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="552" spans="1:19" ht="11" customHeight="1">
+    <row r="552" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A552" s="4" t="s">
         <v>173</v>
       </c>
@@ -33156,7 +33159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553" spans="1:19" ht="11" customHeight="1">
+    <row r="553" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A553" s="4" t="s">
         <v>173</v>
       </c>
@@ -33212,7 +33215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554" spans="1:19" ht="11" customHeight="1">
+    <row r="554" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A554" s="4" t="s">
         <v>173</v>
       </c>
@@ -33271,7 +33274,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="555" spans="1:19" ht="11" customHeight="1">
+    <row r="555" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A555" s="4" t="s">
         <v>173</v>
       </c>
@@ -33327,7 +33330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556" spans="1:19" ht="11" customHeight="1">
+    <row r="556" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A556" s="4" t="s">
         <v>173</v>
       </c>
@@ -33383,7 +33386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557" spans="1:19" ht="11" customHeight="1">
+    <row r="557" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A557" s="4" t="s">
         <v>173</v>
       </c>
@@ -33442,7 +33445,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:19" ht="11" customHeight="1">
+    <row r="558" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A558" s="4" t="s">
         <v>173</v>
       </c>
@@ -33498,7 +33501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:19" ht="11" customHeight="1">
+    <row r="559" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A559" s="4" t="s">
         <v>173</v>
       </c>
@@ -33554,7 +33557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="560" spans="1:19" ht="11" customHeight="1">
+    <row r="560" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A560" s="4" t="s">
         <v>173</v>
       </c>
@@ -33613,7 +33616,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="561" spans="1:19" ht="11" customHeight="1">
+    <row r="561" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A561" s="4" t="s">
         <v>173</v>
       </c>
@@ -33672,7 +33675,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="562" spans="1:19" ht="11" customHeight="1">
+    <row r="562" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A562" s="4" t="s">
         <v>173</v>
       </c>
@@ -33731,7 +33734,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="563" spans="1:19" ht="11" customHeight="1">
+    <row r="563" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A563" s="4" t="s">
         <v>173</v>
       </c>
@@ -33787,7 +33790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564" spans="1:19" ht="11" customHeight="1">
+    <row r="564" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A564" s="4" t="s">
         <v>173</v>
       </c>
@@ -33843,7 +33846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:19" ht="11" customHeight="1">
+    <row r="565" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A565" s="4" t="s">
         <v>173</v>
       </c>
@@ -33899,7 +33902,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="566" spans="1:19" ht="11" customHeight="1">
+    <row r="566" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A566" s="4" t="s">
         <v>173</v>
       </c>
@@ -33955,7 +33958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567" spans="1:19" ht="11" customHeight="1">
+    <row r="567" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A567" s="4" t="s">
         <v>173</v>
       </c>
@@ -34005,7 +34008,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="568" spans="1:19" ht="11" customHeight="1">
+    <row r="568" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A568" s="4" t="s">
         <v>173</v>
       </c>
@@ -34055,7 +34058,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="569" spans="1:19" ht="11" customHeight="1">
+    <row r="569" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A569" s="4" t="s">
         <v>173</v>
       </c>
@@ -34111,7 +34114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:19" ht="11" customHeight="1">
+    <row r="570" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A570" s="4" t="s">
         <v>173</v>
       </c>
@@ -34167,7 +34170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:19" ht="11" customHeight="1">
+    <row r="571" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A571" s="4" t="s">
         <v>173</v>
       </c>
@@ -34223,7 +34226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:19" ht="11" customHeight="1">
+    <row r="572" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A572" s="4" t="s">
         <v>173</v>
       </c>
@@ -34279,7 +34282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573" spans="1:19" ht="11" customHeight="1">
+    <row r="573" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A573" s="4" t="s">
         <v>173</v>
       </c>
@@ -34335,7 +34338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574" spans="1:19" ht="11" customHeight="1">
+    <row r="574" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A574" s="4" t="s">
         <v>173</v>
       </c>
@@ -34391,7 +34394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575" spans="1:19" ht="11" customHeight="1">
+    <row r="575" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A575" s="4" t="s">
         <v>173</v>
       </c>
@@ -34447,7 +34450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:19" ht="11" customHeight="1">
+    <row r="576" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A576" s="4" t="s">
         <v>173</v>
       </c>
@@ -34503,7 +34506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:19" ht="11" customHeight="1">
+    <row r="577" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A577" s="4" t="s">
         <v>173</v>
       </c>
@@ -34562,7 +34565,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="578" spans="1:19" ht="11" customHeight="1">
+    <row r="578" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A578" s="4" t="s">
         <v>173</v>
       </c>
@@ -34618,7 +34621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579" spans="1:19" ht="11" customHeight="1">
+    <row r="579" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A579" s="4" t="s">
         <v>173</v>
       </c>
@@ -34674,7 +34677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580" spans="1:19" ht="11" customHeight="1">
+    <row r="580" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A580" s="4" t="s">
         <v>173</v>
       </c>
@@ -34730,7 +34733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:19" ht="11" customHeight="1">
+    <row r="581" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A581" s="4" t="s">
         <v>173</v>
       </c>
@@ -34786,7 +34789,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="582" spans="1:19" ht="11" customHeight="1">
+    <row r="582" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A582" s="4" t="s">
         <v>173</v>
       </c>
@@ -34845,7 +34848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="583" spans="1:19" ht="11" customHeight="1">
+    <row r="583" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A583" s="4" t="s">
         <v>173</v>
       </c>
@@ -34901,7 +34904,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="584" spans="1:19" ht="11" customHeight="1">
+    <row r="584" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A584" s="4" t="s">
         <v>173</v>
       </c>
@@ -34960,7 +34963,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="585" spans="1:19" ht="11" customHeight="1">
+    <row r="585" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A585" s="4" t="s">
         <v>173</v>
       </c>
@@ -35016,7 +35019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586" spans="1:19" ht="11" customHeight="1">
+    <row r="586" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A586" s="4" t="s">
         <v>173</v>
       </c>
@@ -35072,7 +35075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587" spans="1:19" ht="11" customHeight="1">
+    <row r="587" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A587" s="4" t="s">
         <v>173</v>
       </c>
@@ -35128,7 +35131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:19" ht="11" customHeight="1">
+    <row r="588" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A588" s="4" t="s">
         <v>173</v>
       </c>
@@ -35184,7 +35187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:19" ht="11" customHeight="1">
+    <row r="589" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A589" s="4" t="s">
         <v>173</v>
       </c>
@@ -35234,7 +35237,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="590" spans="1:19" ht="11" customHeight="1">
+    <row r="590" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A590" s="4" t="s">
         <v>173</v>
       </c>
@@ -35293,7 +35296,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:19" ht="11" customHeight="1">
+    <row r="591" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A591" s="4" t="s">
         <v>173</v>
       </c>
@@ -35349,7 +35352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592" spans="1:19" ht="11" customHeight="1">
+    <row r="592" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A592" s="4" t="s">
         <v>173</v>
       </c>
@@ -35405,7 +35408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:19" ht="11" customHeight="1">
+    <row r="593" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A593" s="4" t="s">
         <v>173</v>
       </c>
@@ -35461,7 +35464,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="594" spans="1:19" ht="11" customHeight="1">
+    <row r="594" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A594" s="4" t="s">
         <v>173</v>
       </c>
@@ -35517,7 +35520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="595" spans="1:19" ht="11" customHeight="1">
+    <row r="595" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A595" s="4" t="s">
         <v>173</v>
       </c>
@@ -35573,7 +35576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596" spans="1:19" ht="11" customHeight="1">
+    <row r="596" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A596" s="4" t="s">
         <v>173</v>
       </c>
@@ -35623,7 +35626,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="597" spans="1:19" ht="11" customHeight="1">
+    <row r="597" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A597" s="4" t="s">
         <v>173</v>
       </c>
@@ -35679,7 +35682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:19" ht="11" customHeight="1">
+    <row r="598" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A598" s="4" t="s">
         <v>173</v>
       </c>
@@ -35735,7 +35738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:19" ht="11" customHeight="1">
+    <row r="599" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A599" s="4" t="s">
         <v>173</v>
       </c>
@@ -35791,7 +35794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:19" ht="11" customHeight="1">
+    <row r="600" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A600" s="4" t="s">
         <v>173</v>
       </c>
@@ -35847,7 +35850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:19" ht="11" customHeight="1">
+    <row r="601" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A601" s="4" t="s">
         <v>173</v>
       </c>
@@ -35903,7 +35906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602" spans="1:19" ht="11" customHeight="1">
+    <row r="602" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A602" s="4" t="s">
         <v>173</v>
       </c>
@@ -35959,7 +35962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:19" ht="11" customHeight="1">
+    <row r="603" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A603" s="4" t="s">
         <v>173</v>
       </c>
@@ -36018,7 +36021,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="604" spans="1:19" ht="11" customHeight="1">
+    <row r="604" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A604" s="4" t="s">
         <v>173</v>
       </c>
@@ -36074,7 +36077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="605" spans="1:19" ht="11" customHeight="1">
+    <row r="605" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A605" s="4" t="s">
         <v>173</v>
       </c>
@@ -36130,7 +36133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606" spans="1:19" ht="11" customHeight="1">
+    <row r="606" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A606" s="4" t="s">
         <v>173</v>
       </c>
@@ -36186,7 +36189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607" spans="1:19" ht="11" customHeight="1">
+    <row r="607" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A607" s="4" t="s">
         <v>173</v>
       </c>
@@ -36242,7 +36245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608" spans="1:19" ht="11" customHeight="1">
+    <row r="608" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A608" s="4" t="s">
         <v>173</v>
       </c>
@@ -36298,7 +36301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609" spans="1:19" ht="11" customHeight="1">
+    <row r="609" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A609" s="4" t="s">
         <v>173</v>
       </c>
@@ -36357,7 +36360,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="610" spans="1:19" ht="11" customHeight="1">
+    <row r="610" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A610" s="4" t="s">
         <v>173</v>
       </c>
@@ -36413,7 +36416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611" spans="1:19" ht="11" customHeight="1">
+    <row r="611" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A611" s="4" t="s">
         <v>173</v>
       </c>
@@ -36469,7 +36472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:19" ht="11" customHeight="1">
+    <row r="612" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A612" s="4" t="s">
         <v>173</v>
       </c>
@@ -36525,7 +36528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613" spans="1:19" ht="11" customHeight="1">
+    <row r="613" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A613" s="4" t="s">
         <v>173</v>
       </c>
@@ -36584,7 +36587,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="614" spans="1:19" ht="11" customHeight="1">
+    <row r="614" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A614" s="4" t="s">
         <v>173</v>
       </c>
@@ -36640,7 +36643,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="615" spans="1:19" ht="11" customHeight="1">
+    <row r="615" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A615" s="4" t="s">
         <v>173</v>
       </c>
@@ -36696,7 +36699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:19" ht="11" customHeight="1">
+    <row r="616" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A616" s="4" t="s">
         <v>173</v>
       </c>
@@ -36752,7 +36755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:19" ht="11" customHeight="1">
+    <row r="617" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A617" s="4" t="s">
         <v>173</v>
       </c>
@@ -36808,7 +36811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:19" ht="11" customHeight="1">
+    <row r="618" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A618" s="4" t="s">
         <v>173</v>
       </c>
@@ -36864,7 +36867,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="619" spans="1:19" ht="11" customHeight="1">
+    <row r="619" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A619" s="4" t="s">
         <v>173</v>
       </c>
@@ -36920,7 +36923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620" spans="1:19" ht="11" customHeight="1">
+    <row r="620" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A620" s="4" t="s">
         <v>173</v>
       </c>
@@ -36976,7 +36979,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:19" ht="11" customHeight="1">
+    <row r="621" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A621" s="4" t="s">
         <v>173</v>
       </c>
@@ -37032,7 +37035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622" spans="1:19" ht="11" customHeight="1">
+    <row r="622" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A622" s="4" t="s">
         <v>173</v>
       </c>
@@ -37088,7 +37091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:19" ht="11" customHeight="1">
+    <row r="623" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A623" s="4" t="s">
         <v>173</v>
       </c>
@@ -37144,7 +37147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624" spans="1:19" ht="11" customHeight="1">
+    <row r="624" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A624" s="4" t="s">
         <v>173</v>
       </c>
@@ -37194,7 +37197,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="625" spans="1:19" ht="11" customHeight="1">
+    <row r="625" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A625" s="4" t="s">
         <v>173</v>
       </c>
@@ -37253,7 +37256,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="626" spans="1:19" ht="11" customHeight="1">
+    <row r="626" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A626" s="4" t="s">
         <v>173</v>
       </c>
@@ -37309,7 +37312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:19" ht="11" customHeight="1">
+    <row r="627" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A627" s="4" t="s">
         <v>173</v>
       </c>
@@ -37365,7 +37368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:19" ht="11" customHeight="1">
+    <row r="628" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A628" s="4" t="s">
         <v>173</v>
       </c>
@@ -37415,7 +37418,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="629" spans="1:19" ht="11" customHeight="1">
+    <row r="629" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A629" s="4" t="s">
         <v>173</v>
       </c>
@@ -37474,7 +37477,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="630" spans="1:19" ht="11" customHeight="1">
+    <row r="630" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A630" s="4" t="s">
         <v>173</v>
       </c>
@@ -37512,7 +37515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:19" ht="11" customHeight="1">
+    <row r="631" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A631" s="4" t="s">
         <v>173</v>
       </c>
@@ -37571,7 +37574,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="632" spans="1:19" ht="11" customHeight="1">
+    <row r="632" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A632" s="4" t="s">
         <v>173</v>
       </c>
@@ -37630,7 +37633,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="633" spans="1:19" ht="11" customHeight="1">
+    <row r="633" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A633" s="4" t="s">
         <v>173</v>
       </c>
@@ -37686,7 +37689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634" spans="1:19" ht="11" customHeight="1">
+    <row r="634" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A634" s="4" t="s">
         <v>173</v>
       </c>
@@ -37742,7 +37745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635" spans="1:19" ht="11" customHeight="1">
+    <row r="635" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A635" s="4" t="s">
         <v>173</v>
       </c>
@@ -37798,7 +37801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636" spans="1:19" ht="11" customHeight="1">
+    <row r="636" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A636" s="4" t="s">
         <v>173</v>
       </c>
@@ -37857,7 +37860,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="637" spans="1:19" ht="11" customHeight="1">
+    <row r="637" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A637" s="4" t="s">
         <v>173</v>
       </c>
@@ -37907,7 +37910,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="638" spans="1:19" ht="11" customHeight="1">
+    <row r="638" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A638" s="4" t="s">
         <v>173</v>
       </c>
@@ -37963,7 +37966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="639" spans="1:19" ht="11" customHeight="1">
+    <row r="639" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A639" s="4" t="s">
         <v>173</v>
       </c>
@@ -38022,7 +38025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="640" spans="1:19" ht="11" customHeight="1">
+    <row r="640" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A640" s="4" t="s">
         <v>173</v>
       </c>
@@ -38078,7 +38081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641" spans="1:19" ht="11" customHeight="1">
+    <row r="641" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A641" s="4" t="s">
         <v>173</v>
       </c>
@@ -38134,7 +38137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="642" spans="1:19" ht="11" customHeight="1">
+    <row r="642" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A642" s="4" t="s">
         <v>173</v>
       </c>
@@ -38190,7 +38193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643" spans="1:19" ht="11" customHeight="1">
+    <row r="643" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A643" s="4" t="s">
         <v>173</v>
       </c>
@@ -38246,7 +38249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:19" ht="11" customHeight="1">
+    <row r="644" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A644" s="4" t="s">
         <v>173</v>
       </c>
@@ -38302,7 +38305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645" spans="1:19" ht="11" customHeight="1">
+    <row r="645" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A645" s="4" t="s">
         <v>173</v>
       </c>
@@ -38358,7 +38361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646" spans="1:19" ht="11" customHeight="1">
+    <row r="646" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A646" s="4" t="s">
         <v>173</v>
       </c>
@@ -38408,7 +38411,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="647" spans="1:19" ht="11" customHeight="1">
+    <row r="647" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A647" s="4" t="s">
         <v>173</v>
       </c>
@@ -38458,7 +38461,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="648" spans="1:19" ht="11" customHeight="1">
+    <row r="648" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A648" s="4" t="s">
         <v>173</v>
       </c>
@@ -38514,7 +38517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="649" spans="1:19" ht="11" customHeight="1">
+    <row r="649" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A649" s="4" t="s">
         <v>173</v>
       </c>
@@ -38570,7 +38573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650" spans="1:19" ht="11" customHeight="1">
+    <row r="650" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A650" s="4" t="s">
         <v>173</v>
       </c>
@@ -38626,7 +38629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:19" ht="11" customHeight="1">
+    <row r="651" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A651" s="4" t="s">
         <v>173</v>
       </c>
@@ -38682,7 +38685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="652" spans="1:19" ht="11" customHeight="1">
+    <row r="652" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A652" s="4" t="s">
         <v>173</v>
       </c>
@@ -38738,7 +38741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="653" spans="1:19" ht="11" customHeight="1">
+    <row r="653" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A653" s="4" t="s">
         <v>173</v>
       </c>
@@ -38797,7 +38800,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="654" spans="1:19" ht="11" customHeight="1">
+    <row r="654" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A654" s="4" t="s">
         <v>173</v>
       </c>
@@ -38853,7 +38856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:19" ht="11" customHeight="1">
+    <row r="655" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A655" s="4" t="s">
         <v>173</v>
       </c>
@@ -38909,7 +38912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:19" ht="11" customHeight="1">
+    <row r="656" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A656" s="4" t="s">
         <v>173</v>
       </c>
@@ -38968,7 +38971,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:19" ht="11" customHeight="1">
+    <row r="657" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A657" s="4" t="s">
         <v>173</v>
       </c>
@@ -39024,7 +39027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:19" ht="11" customHeight="1">
+    <row r="658" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A658" s="4" t="s">
         <v>173</v>
       </c>
@@ -39083,7 +39086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:19" ht="11" customHeight="1">
+    <row r="659" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A659" s="4" t="s">
         <v>173</v>
       </c>
@@ -39139,7 +39142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="660" spans="1:19" ht="11" customHeight="1">
+    <row r="660" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A660" s="4" t="s">
         <v>173</v>
       </c>
@@ -39195,7 +39198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="661" spans="1:19" ht="11" customHeight="1">
+    <row r="661" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A661" s="4" t="s">
         <v>173</v>
       </c>
@@ -39254,7 +39257,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="662" spans="1:19" ht="11" customHeight="1">
+    <row r="662" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A662" s="4" t="s">
         <v>173</v>
       </c>
@@ -39310,7 +39313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="663" spans="1:19" ht="11" customHeight="1">
+    <row r="663" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A663" s="4" t="s">
         <v>173</v>
       </c>
@@ -39366,7 +39369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="664" spans="1:19" ht="11" customHeight="1">
+    <row r="664" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A664" s="4" t="s">
         <v>173</v>
       </c>
@@ -39425,7 +39428,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="665" spans="1:19" ht="11" customHeight="1">
+    <row r="665" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A665" s="4" t="s">
         <v>173</v>
       </c>
@@ -39484,7 +39487,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="666" spans="1:19" ht="11" customHeight="1">
+    <row r="666" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A666" s="4" t="s">
         <v>173</v>
       </c>
@@ -39540,7 +39543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="667" spans="1:19" ht="11" customHeight="1">
+    <row r="667" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A667" s="4" t="s">
         <v>173</v>
       </c>
@@ -39590,7 +39593,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="668" spans="1:19" ht="11" customHeight="1">
+    <row r="668" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A668" s="4" t="s">
         <v>173</v>
       </c>
@@ -39646,7 +39649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:19" ht="11" customHeight="1">
+    <row r="669" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A669" s="4" t="s">
         <v>173</v>
       </c>
@@ -39696,7 +39699,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="670" spans="1:19" ht="11" customHeight="1">
+    <row r="670" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A670" s="4" t="s">
         <v>173</v>
       </c>
@@ -39752,7 +39755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="671" spans="1:19" ht="11" customHeight="1">
+    <row r="671" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A671" s="4" t="s">
         <v>173</v>
       </c>
@@ -39808,7 +39811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="672" spans="1:19" ht="11" customHeight="1">
+    <row r="672" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A672" s="4" t="s">
         <v>173</v>
       </c>
@@ -39864,7 +39867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="673" spans="1:19" ht="11" customHeight="1">
+    <row r="673" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A673" s="4" t="s">
         <v>173</v>
       </c>
@@ -39920,7 +39923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="674" spans="1:19" ht="11" customHeight="1">
+    <row r="674" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A674" s="4" t="s">
         <v>173</v>
       </c>
@@ -39976,7 +39979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:19" ht="11" customHeight="1">
+    <row r="675" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A675" s="4" t="s">
         <v>173</v>
       </c>
@@ -40035,7 +40038,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="676" spans="1:19" ht="11" customHeight="1">
+    <row r="676" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A676" s="4" t="s">
         <v>173</v>
       </c>
@@ -40091,7 +40094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="677" spans="1:19" ht="11" customHeight="1">
+    <row r="677" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A677" s="4" t="s">
         <v>173</v>
       </c>
@@ -40147,7 +40150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="678" spans="1:19" ht="11" customHeight="1">
+    <row r="678" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A678" s="4" t="s">
         <v>173</v>
       </c>
@@ -40203,7 +40206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:19" ht="11" customHeight="1">
+    <row r="679" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A679" s="4" t="s">
         <v>173</v>
       </c>
@@ -40259,7 +40262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680" spans="1:19" ht="11" customHeight="1">
+    <row r="680" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A680" s="4" t="s">
         <v>173</v>
       </c>
@@ -40315,7 +40318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:19" ht="11" customHeight="1">
+    <row r="681" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A681" s="4" t="s">
         <v>173</v>
       </c>
@@ -40371,7 +40374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="682" spans="1:19" ht="11" customHeight="1">
+    <row r="682" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A682" s="4" t="s">
         <v>173</v>
       </c>
@@ -40430,7 +40433,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="683" spans="1:19" ht="11" customHeight="1">
+    <row r="683" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A683" s="4" t="s">
         <v>173</v>
       </c>
@@ -40486,7 +40489,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="684" spans="1:19" ht="11" customHeight="1">
+    <row r="684" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A684" s="4" t="s">
         <v>173</v>
       </c>
@@ -40542,7 +40545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:19" ht="11" customHeight="1">
+    <row r="685" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A685" s="4" t="s">
         <v>173</v>
       </c>
@@ -40598,7 +40601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:19" ht="11" customHeight="1">
+    <row r="686" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A686" s="4" t="s">
         <v>173</v>
       </c>
@@ -40648,7 +40651,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="687" spans="1:19" ht="11" customHeight="1">
+    <row r="687" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A687" s="4" t="s">
         <v>173</v>
       </c>
@@ -40707,7 +40710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:19" ht="11" customHeight="1">
+    <row r="688" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A688" s="4" t="s">
         <v>173</v>
       </c>
@@ -40763,7 +40766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="689" spans="1:19" ht="11" customHeight="1">
+    <row r="689" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A689" s="4" t="s">
         <v>173</v>
       </c>
@@ -40819,7 +40822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="690" spans="1:19" ht="11" customHeight="1">
+    <row r="690" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A690" s="4" t="s">
         <v>173</v>
       </c>
@@ -40875,7 +40878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:19" ht="11" customHeight="1">
+    <row r="691" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A691" s="4" t="s">
         <v>173</v>
       </c>
@@ -40934,7 +40937,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="692" spans="1:19" ht="11" customHeight="1">
+    <row r="692" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A692" s="4" t="s">
         <v>173</v>
       </c>
@@ -40990,7 +40993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="693" spans="1:19" ht="11" customHeight="1">
+    <row r="693" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A693" s="4" t="s">
         <v>199</v>
       </c>
@@ -41049,7 +41052,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="694" spans="1:19" ht="11" customHeight="1">
+    <row r="694" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A694" s="4" t="s">
         <v>199</v>
       </c>
@@ -41106,7 +41109,7 @@
       </c>
       <c r="S694" s="6"/>
     </row>
-    <row r="695" spans="1:19" ht="11" customHeight="1">
+    <row r="695" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A695" s="4" t="s">
         <v>199</v>
       </c>
@@ -41156,7 +41159,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="696" spans="1:19" ht="11" customHeight="1">
+    <row r="696" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A696" s="4" t="s">
         <v>199</v>
       </c>
@@ -41215,7 +41218,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="697" spans="1:19" ht="11" customHeight="1">
+    <row r="697" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A697" s="4" t="s">
         <v>199</v>
       </c>
@@ -41274,7 +41277,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="698" spans="1:19" ht="11" customHeight="1">
+    <row r="698" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A698" s="4" t="s">
         <v>199</v>
       </c>
@@ -41331,7 +41334,7 @@
       </c>
       <c r="S698" s="6"/>
     </row>
-    <row r="699" spans="1:19" ht="11" customHeight="1">
+    <row r="699" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A699" s="4" t="s">
         <v>199</v>
       </c>
@@ -41390,7 +41393,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="700" spans="1:19" ht="11" customHeight="1">
+    <row r="700" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A700" s="4" t="s">
         <v>199</v>
       </c>
@@ -41447,7 +41450,7 @@
       </c>
       <c r="S700" s="6"/>
     </row>
-    <row r="701" spans="1:19" ht="11" customHeight="1">
+    <row r="701" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A701" s="4" t="s">
         <v>199</v>
       </c>
@@ -41506,7 +41509,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="702" spans="1:19" ht="11" customHeight="1">
+    <row r="702" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A702" s="4" t="s">
         <v>199</v>
       </c>
@@ -41563,7 +41566,7 @@
       </c>
       <c r="S702" s="6"/>
     </row>
-    <row r="703" spans="1:19" ht="11" customHeight="1">
+    <row r="703" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A703" s="4" t="s">
         <v>199</v>
       </c>
@@ -41620,7 +41623,7 @@
       </c>
       <c r="S703" s="6"/>
     </row>
-    <row r="704" spans="1:19" ht="11" customHeight="1">
+    <row r="704" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A704" s="4" t="s">
         <v>199</v>
       </c>
@@ -41677,7 +41680,7 @@
       </c>
       <c r="S704" s="6"/>
     </row>
-    <row r="705" spans="1:19" ht="11" customHeight="1">
+    <row r="705" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A705" s="4" t="s">
         <v>199</v>
       </c>
@@ -41736,7 +41739,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="706" spans="1:19" ht="11" customHeight="1">
+    <row r="706" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A706" s="4" t="s">
         <v>199</v>
       </c>
@@ -41795,7 +41798,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="707" spans="1:19" ht="11" customHeight="1">
+    <row r="707" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A707" s="4" t="s">
         <v>199</v>
       </c>
@@ -41852,7 +41855,7 @@
       </c>
       <c r="S707" s="6"/>
     </row>
-    <row r="708" spans="1:19" ht="11" customHeight="1">
+    <row r="708" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A708" s="4" t="s">
         <v>199</v>
       </c>
@@ -41909,7 +41912,7 @@
       </c>
       <c r="S708" s="6"/>
     </row>
-    <row r="709" spans="1:19" ht="11" customHeight="1">
+    <row r="709" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A709" s="4" t="s">
         <v>199</v>
       </c>
@@ -41966,7 +41969,7 @@
       </c>
       <c r="S709" s="6"/>
     </row>
-    <row r="710" spans="1:19" ht="11" customHeight="1">
+    <row r="710" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A710" s="4" t="s">
         <v>199</v>
       </c>
@@ -42023,7 +42026,7 @@
       </c>
       <c r="S710" s="6"/>
     </row>
-    <row r="711" spans="1:19" ht="11" customHeight="1">
+    <row r="711" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A711" s="4" t="s">
         <v>199</v>
       </c>
@@ -42080,7 +42083,7 @@
       </c>
       <c r="S711" s="6"/>
     </row>
-    <row r="712" spans="1:19" ht="11" customHeight="1">
+    <row r="712" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A712" s="4" t="s">
         <v>199</v>
       </c>
@@ -42137,7 +42140,7 @@
       </c>
       <c r="S712" s="6"/>
     </row>
-    <row r="713" spans="1:19" ht="11" customHeight="1">
+    <row r="713" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A713" s="4" t="s">
         <v>199</v>
       </c>
@@ -42194,7 +42197,7 @@
       </c>
       <c r="S713" s="6"/>
     </row>
-    <row r="714" spans="1:19" ht="11" customHeight="1">
+    <row r="714" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A714" s="4" t="s">
         <v>199</v>
       </c>
@@ -42251,7 +42254,7 @@
       </c>
       <c r="S714" s="6"/>
     </row>
-    <row r="715" spans="1:19" ht="11" customHeight="1">
+    <row r="715" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A715" s="4" t="s">
         <v>199</v>
       </c>
@@ -42310,7 +42313,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="716" spans="1:19" ht="11" customHeight="1">
+    <row r="716" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A716" s="4" t="s">
         <v>199</v>
       </c>
@@ -42369,7 +42372,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="717" spans="1:19" ht="11" customHeight="1">
+    <row r="717" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A717" s="4" t="s">
         <v>199</v>
       </c>
@@ -42428,7 +42431,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="718" spans="1:19" ht="11" customHeight="1">
+    <row r="718" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A718" s="4" t="s">
         <v>199</v>
       </c>
@@ -42476,7 +42479,7 @@
       </c>
       <c r="S718" s="6"/>
     </row>
-    <row r="719" spans="1:19" ht="11" customHeight="1">
+    <row r="719" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A719" s="4" t="s">
         <v>199</v>
       </c>
@@ -42526,7 +42529,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="720" spans="1:19" ht="11" customHeight="1">
+    <row r="720" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A720" s="4" t="s">
         <v>199</v>
       </c>
@@ -42583,7 +42586,7 @@
       </c>
       <c r="S720" s="6"/>
     </row>
-    <row r="721" spans="1:19" ht="11" customHeight="1">
+    <row r="721" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A721" s="4" t="s">
         <v>199</v>
       </c>
@@ -42640,7 +42643,7 @@
       </c>
       <c r="S721" s="6"/>
     </row>
-    <row r="722" spans="1:19" ht="11" customHeight="1">
+    <row r="722" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A722" s="4" t="s">
         <v>199</v>
       </c>
@@ -42699,7 +42702,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="723" spans="1:19" ht="11" customHeight="1">
+    <row r="723" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A723" s="4" t="s">
         <v>199</v>
       </c>
@@ -42756,7 +42759,7 @@
       </c>
       <c r="S723" s="6"/>
     </row>
-    <row r="724" spans="1:19" ht="11" customHeight="1">
+    <row r="724" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A724" s="4" t="s">
         <v>199</v>
       </c>
@@ -42815,7 +42818,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="725" spans="1:19" ht="11" customHeight="1">
+    <row r="725" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A725" s="4" t="s">
         <v>199</v>
       </c>
@@ -42865,7 +42868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="726" spans="1:19" ht="11" customHeight="1">
+    <row r="726" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A726" s="4" t="s">
         <v>199</v>
       </c>
@@ -42924,7 +42927,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="727" spans="1:19" ht="11" customHeight="1">
+    <row r="727" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A727" s="4" t="s">
         <v>199</v>
       </c>
@@ -42981,7 +42984,7 @@
       </c>
       <c r="S727" s="6"/>
     </row>
-    <row r="728" spans="1:19" ht="11" customHeight="1">
+    <row r="728" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A728" s="4" t="s">
         <v>199</v>
       </c>
@@ -43040,7 +43043,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="729" spans="1:19" ht="11" customHeight="1">
+    <row r="729" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A729" s="4" t="s">
         <v>199</v>
       </c>
@@ -43097,7 +43100,7 @@
       </c>
       <c r="S729" s="6"/>
     </row>
-    <row r="730" spans="1:19" ht="11" customHeight="1">
+    <row r="730" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A730" s="4" t="s">
         <v>199</v>
       </c>
@@ -43156,7 +43159,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="731" spans="1:19" ht="11" customHeight="1">
+    <row r="731" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A731" s="4" t="s">
         <v>199</v>
       </c>
@@ -43213,7 +43216,7 @@
       </c>
       <c r="S731" s="6"/>
     </row>
-    <row r="732" spans="1:19" ht="11" customHeight="1">
+    <row r="732" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A732" s="4" t="s">
         <v>199</v>
       </c>
@@ -43272,7 +43275,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="733" spans="1:19" ht="11" customHeight="1">
+    <row r="733" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A733" s="4" t="s">
         <v>199</v>
       </c>
@@ -43329,7 +43332,7 @@
       </c>
       <c r="S733" s="6"/>
     </row>
-    <row r="734" spans="1:19" ht="11" customHeight="1">
+    <row r="734" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A734" s="4" t="s">
         <v>199</v>
       </c>
@@ -43386,7 +43389,7 @@
       </c>
       <c r="S734" s="6"/>
     </row>
-    <row r="735" spans="1:19" ht="11" customHeight="1">
+    <row r="735" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A735" s="4" t="s">
         <v>199</v>
       </c>
@@ -43445,7 +43448,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="736" spans="1:19" ht="11" customHeight="1">
+    <row r="736" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A736" s="4" t="s">
         <v>199</v>
       </c>
@@ -43502,7 +43505,7 @@
       </c>
       <c r="S736" s="6"/>
     </row>
-    <row r="737" spans="1:19" ht="11" customHeight="1">
+    <row r="737" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A737" s="4" t="s">
         <v>199</v>
       </c>
@@ -43561,7 +43564,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="738" spans="1:19" ht="11" customHeight="1">
+    <row r="738" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A738" s="4" t="s">
         <v>199</v>
       </c>
@@ -43618,7 +43621,7 @@
       </c>
       <c r="S738" s="6"/>
     </row>
-    <row r="739" spans="1:19" ht="11" customHeight="1">
+    <row r="739" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A739" s="4" t="s">
         <v>199</v>
       </c>
@@ -43675,7 +43678,7 @@
       </c>
       <c r="S739" s="6"/>
     </row>
-    <row r="740" spans="1:19" ht="11" customHeight="1">
+    <row r="740" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A740" s="4" t="s">
         <v>199</v>
       </c>
@@ -43734,7 +43737,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:19" ht="11" customHeight="1">
+    <row r="741" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A741" s="4" t="s">
         <v>199</v>
       </c>
@@ -43793,7 +43796,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="742" spans="1:19" ht="11" customHeight="1">
+    <row r="742" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A742" s="4" t="s">
         <v>199</v>
       </c>
@@ -43843,7 +43846,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="743" spans="1:19" ht="11" customHeight="1">
+    <row r="743" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A743" s="4" t="s">
         <v>199</v>
       </c>
@@ -43900,7 +43903,7 @@
       </c>
       <c r="S743" s="6"/>
     </row>
-    <row r="744" spans="1:19" ht="11" customHeight="1">
+    <row r="744" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A744" s="4" t="s">
         <v>199</v>
       </c>
@@ -43957,7 +43960,7 @@
       </c>
       <c r="S744" s="6"/>
     </row>
-    <row r="745" spans="1:19" ht="11" customHeight="1">
+    <row r="745" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A745" s="4" t="s">
         <v>199</v>
       </c>
@@ -44014,7 +44017,7 @@
       </c>
       <c r="S745" s="6"/>
     </row>
-    <row r="746" spans="1:19" ht="11" customHeight="1">
+    <row r="746" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A746" s="4" t="s">
         <v>199</v>
       </c>
@@ -44071,7 +44074,7 @@
       </c>
       <c r="S746" s="6"/>
     </row>
-    <row r="747" spans="1:19" ht="11" customHeight="1">
+    <row r="747" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A747" s="4" t="s">
         <v>199</v>
       </c>
@@ -44128,7 +44131,7 @@
       </c>
       <c r="S747" s="6"/>
     </row>
-    <row r="748" spans="1:19" ht="11" customHeight="1">
+    <row r="748" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A748" s="4" t="s">
         <v>199</v>
       </c>
@@ -44185,7 +44188,7 @@
       </c>
       <c r="S748" s="6"/>
     </row>
-    <row r="749" spans="1:19" ht="11" customHeight="1">
+    <row r="749" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A749" s="4" t="s">
         <v>199</v>
       </c>
@@ -44244,7 +44247,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="750" spans="1:19" ht="11" customHeight="1">
+    <row r="750" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A750" s="4" t="s">
         <v>199</v>
       </c>
@@ -44303,7 +44306,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="751" spans="1:19" ht="11" customHeight="1">
+    <row r="751" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A751" s="4" t="s">
         <v>199</v>
       </c>
@@ -44360,7 +44363,7 @@
       </c>
       <c r="S751" s="6"/>
     </row>
-    <row r="752" spans="1:19" ht="11" customHeight="1">
+    <row r="752" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A752" s="4" t="s">
         <v>199</v>
       </c>
@@ -44419,7 +44422,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="753" spans="1:19" ht="11" customHeight="1">
+    <row r="753" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A753" s="4" t="s">
         <v>199</v>
       </c>
@@ -44478,7 +44481,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="754" spans="1:19" ht="11" customHeight="1">
+    <row r="754" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A754" s="4" t="s">
         <v>199</v>
       </c>
@@ -44535,7 +44538,7 @@
       </c>
       <c r="S754" s="6"/>
     </row>
-    <row r="755" spans="1:19" ht="11" customHeight="1">
+    <row r="755" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A755" s="4" t="s">
         <v>199</v>
       </c>
@@ -44594,7 +44597,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="756" spans="1:19" ht="11" customHeight="1">
+    <row r="756" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A756" s="4" t="s">
         <v>199</v>
       </c>
@@ -44653,7 +44656,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="757" spans="1:19" ht="11" customHeight="1">
+    <row r="757" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A757" s="4" t="s">
         <v>199</v>
       </c>
@@ -44710,7 +44713,7 @@
       </c>
       <c r="S757" s="6"/>
     </row>
-    <row r="758" spans="1:19" ht="11" customHeight="1">
+    <row r="758" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A758" s="4" t="s">
         <v>199</v>
       </c>
@@ -44767,7 +44770,7 @@
       </c>
       <c r="S758" s="6"/>
     </row>
-    <row r="759" spans="1:19" ht="11" customHeight="1">
+    <row r="759" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A759" s="4" t="s">
         <v>199</v>
       </c>
@@ -44826,7 +44829,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="760" spans="1:19" ht="11" customHeight="1">
+    <row r="760" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A760" s="4" t="s">
         <v>199</v>
       </c>
@@ -44885,7 +44888,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="761" spans="1:19" ht="11" customHeight="1">
+    <row r="761" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A761" s="4" t="s">
         <v>199</v>
       </c>
@@ -44942,7 +44945,7 @@
       </c>
       <c r="S761" s="6"/>
     </row>
-    <row r="762" spans="1:19" ht="11" customHeight="1">
+    <row r="762" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A762" s="4" t="s">
         <v>199</v>
       </c>
@@ -44999,7 +45002,7 @@
       </c>
       <c r="S762" s="6"/>
     </row>
-    <row r="763" spans="1:19" ht="11" customHeight="1">
+    <row r="763" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A763" s="4" t="s">
         <v>199</v>
       </c>
@@ -45024,6 +45027,9 @@
       <c r="H763" s="4" t="s">
         <v>245</v>
       </c>
+      <c r="I763" s="4">
+        <v>0</v>
+      </c>
       <c r="J763" s="4">
         <v>35</v>
       </c>
@@ -45055,7 +45061,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="764" spans="1:19" ht="11" customHeight="1">
+    <row r="764" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A764" s="4" t="s">
         <v>199</v>
       </c>
@@ -45114,7 +45120,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="765" spans="1:19" ht="11" customHeight="1">
+    <row r="765" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A765" s="4" t="s">
         <v>199</v>
       </c>
@@ -45164,7 +45170,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="766" spans="1:19" ht="11" customHeight="1">
+    <row r="766" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A766" s="4" t="s">
         <v>199</v>
       </c>
@@ -45221,7 +45227,7 @@
       </c>
       <c r="S766" s="6"/>
     </row>
-    <row r="767" spans="1:19" ht="11" customHeight="1">
+    <row r="767" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A767" s="4" t="s">
         <v>199</v>
       </c>
@@ -45280,7 +45286,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="768" spans="1:19" ht="11" customHeight="1">
+    <row r="768" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A768" s="4" t="s">
         <v>199</v>
       </c>
@@ -45337,7 +45343,7 @@
       </c>
       <c r="S768" s="6"/>
     </row>
-    <row r="769" spans="1:19" ht="11" customHeight="1">
+    <row r="769" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A769" s="4" t="s">
         <v>199</v>
       </c>
@@ -45396,7 +45402,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="770" spans="1:19" ht="11" customHeight="1">
+    <row r="770" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A770" s="4" t="s">
         <v>199</v>
       </c>
@@ -45455,7 +45461,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="771" spans="1:19" ht="11" customHeight="1">
+    <row r="771" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A771" s="4" t="s">
         <v>199</v>
       </c>
@@ -45514,7 +45520,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="772" spans="1:19" ht="11" customHeight="1">
+    <row r="772" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A772" s="4" t="s">
         <v>199</v>
       </c>
@@ -45571,7 +45577,7 @@
       </c>
       <c r="S772" s="6"/>
     </row>
-    <row r="773" spans="1:19" ht="11" customHeight="1">
+    <row r="773" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A773" s="4" t="s">
         <v>199</v>
       </c>
@@ -45630,7 +45636,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="774" spans="1:19" ht="11" customHeight="1">
+    <row r="774" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A774" s="4" t="s">
         <v>199</v>
       </c>
@@ -45689,7 +45695,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="775" spans="1:19" ht="11" customHeight="1">
+    <row r="775" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A775" s="4" t="s">
         <v>199</v>
       </c>
@@ -45746,7 +45752,7 @@
       </c>
       <c r="S775" s="6"/>
     </row>
-    <row r="776" spans="1:19" ht="11" customHeight="1">
+    <row r="776" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A776" s="4" t="s">
         <v>199</v>
       </c>
@@ -45803,7 +45809,7 @@
       </c>
       <c r="S776" s="6"/>
     </row>
-    <row r="777" spans="1:19" ht="11" customHeight="1">
+    <row r="777" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A777" s="4" t="s">
         <v>199</v>
       </c>
@@ -45860,7 +45866,7 @@
       </c>
       <c r="S777" s="6"/>
     </row>
-    <row r="778" spans="1:19" ht="11" customHeight="1">
+    <row r="778" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A778" s="4" t="s">
         <v>199</v>
       </c>
@@ -45919,7 +45925,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="779" spans="1:19" ht="11" customHeight="1">
+    <row r="779" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A779" s="4" t="s">
         <v>199</v>
       </c>
@@ -45969,7 +45975,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="780" spans="1:19" ht="11" customHeight="1">
+    <row r="780" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A780" s="4" t="s">
         <v>199</v>
       </c>
@@ -46028,7 +46034,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="781" spans="1:19" ht="11" customHeight="1">
+    <row r="781" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A781" s="4" t="s">
         <v>199</v>
       </c>
@@ -46085,7 +46091,7 @@
       </c>
       <c r="S781" s="6"/>
     </row>
-    <row r="782" spans="1:19" ht="11" customHeight="1">
+    <row r="782" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A782" s="4" t="s">
         <v>199</v>
       </c>
@@ -46135,7 +46141,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="783" spans="1:19" ht="11" customHeight="1">
+    <row r="783" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A783" s="4" t="s">
         <v>199</v>
       </c>
@@ -46185,7 +46191,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="784" spans="1:19" ht="11" customHeight="1">
+    <row r="784" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A784" s="4" t="s">
         <v>199</v>
       </c>
@@ -46235,7 +46241,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="785" spans="1:19" ht="11" customHeight="1">
+    <row r="785" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A785" s="4" t="s">
         <v>199</v>
       </c>
@@ -46292,7 +46298,7 @@
       </c>
       <c r="S785" s="6"/>
     </row>
-    <row r="786" spans="1:19" ht="11" customHeight="1">
+    <row r="786" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A786" s="4" t="s">
         <v>199</v>
       </c>
@@ -46351,7 +46357,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="787" spans="1:19" ht="11" customHeight="1">
+    <row r="787" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A787" s="4" t="s">
         <v>199</v>
       </c>
@@ -46408,7 +46414,7 @@
       </c>
       <c r="S787" s="6"/>
     </row>
-    <row r="788" spans="1:19" ht="11" customHeight="1">
+    <row r="788" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A788" s="4" t="s">
         <v>199</v>
       </c>
@@ -46465,7 +46471,7 @@
       </c>
       <c r="S788" s="6"/>
     </row>
-    <row r="789" spans="1:19" ht="11" customHeight="1">
+    <row r="789" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A789" s="4" t="s">
         <v>199</v>
       </c>
@@ -46524,7 +46530,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="790" spans="1:19" ht="11" customHeight="1">
+    <row r="790" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A790" s="4" t="s">
         <v>199</v>
       </c>
@@ -46574,7 +46580,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="791" spans="1:19" ht="11" customHeight="1">
+    <row r="791" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A791" s="4" t="s">
         <v>199</v>
       </c>
@@ -46631,7 +46637,7 @@
       </c>
       <c r="S791" s="6"/>
     </row>
-    <row r="792" spans="1:19" ht="11" customHeight="1">
+    <row r="792" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A792" s="4" t="s">
         <v>199</v>
       </c>
@@ -46690,7 +46696,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="793" spans="1:19" ht="11" customHeight="1">
+    <row r="793" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A793" s="4" t="s">
         <v>199</v>
       </c>
@@ -46747,7 +46753,7 @@
       </c>
       <c r="S793" s="6"/>
     </row>
-    <row r="794" spans="1:19" ht="11" customHeight="1">
+    <row r="794" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A794" s="4" t="s">
         <v>199</v>
       </c>
@@ -46804,7 +46810,7 @@
       </c>
       <c r="S794" s="6"/>
     </row>
-    <row r="795" spans="1:19" ht="11" customHeight="1">
+    <row r="795" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A795" s="4" t="s">
         <v>199</v>
       </c>
@@ -46863,7 +46869,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="796" spans="1:19" ht="11" customHeight="1">
+    <row r="796" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A796" s="4" t="s">
         <v>199</v>
       </c>
@@ -46913,7 +46919,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="797" spans="1:19" ht="11" customHeight="1">
+    <row r="797" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A797" s="4" t="s">
         <v>199</v>
       </c>
@@ -46970,7 +46976,7 @@
       </c>
       <c r="S797" s="6"/>
     </row>
-    <row r="798" spans="1:19" ht="11" customHeight="1">
+    <row r="798" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A798" s="4" t="s">
         <v>199</v>
       </c>
@@ -47027,7 +47033,7 @@
       </c>
       <c r="S798" s="6"/>
     </row>
-    <row r="799" spans="1:19" ht="11" customHeight="1">
+    <row r="799" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A799" s="4" t="s">
         <v>199</v>
       </c>
@@ -47084,7 +47090,7 @@
       </c>
       <c r="S799" s="6"/>
     </row>
-    <row r="800" spans="1:19" ht="11" customHeight="1">
+    <row r="800" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A800" s="4" t="s">
         <v>199</v>
       </c>
@@ -47141,7 +47147,7 @@
       </c>
       <c r="S800" s="6"/>
     </row>
-    <row r="801" spans="1:19" ht="11" customHeight="1">
+    <row r="801" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A801" s="4" t="s">
         <v>199</v>
       </c>
@@ -47198,7 +47204,7 @@
       </c>
       <c r="S801" s="6"/>
     </row>
-    <row r="802" spans="1:19" ht="11" customHeight="1">
+    <row r="802" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A802" s="4" t="s">
         <v>199</v>
       </c>
@@ -47255,7 +47261,7 @@
       </c>
       <c r="S802" s="6"/>
     </row>
-    <row r="803" spans="1:19" ht="11" customHeight="1">
+    <row r="803" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A803" s="4" t="s">
         <v>199</v>
       </c>
@@ -47312,7 +47318,7 @@
       </c>
       <c r="S803" s="6"/>
     </row>
-    <row r="804" spans="1:19" ht="11" customHeight="1">
+    <row r="804" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A804" s="4" t="s">
         <v>199</v>
       </c>
@@ -47369,7 +47375,7 @@
       </c>
       <c r="S804" s="6"/>
     </row>
-    <row r="805" spans="1:19" ht="11" customHeight="1">
+    <row r="805" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A805" s="4" t="s">
         <v>199</v>
       </c>
@@ -47426,7 +47432,7 @@
       </c>
       <c r="S805" s="6"/>
     </row>
-    <row r="806" spans="1:19" ht="11" customHeight="1">
+    <row r="806" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A806" s="4" t="s">
         <v>199</v>
       </c>
@@ -47476,7 +47482,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="807" spans="1:19" ht="11" customHeight="1">
+    <row r="807" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A807" s="4" t="s">
         <v>199</v>
       </c>
@@ -47526,7 +47532,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="808" spans="1:19" ht="11" customHeight="1">
+    <row r="808" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A808" s="4" t="s">
         <v>199</v>
       </c>
@@ -47585,7 +47591,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="809" spans="1:19" ht="11" customHeight="1">
+    <row r="809" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A809" s="4" t="s">
         <v>199</v>
       </c>
@@ -47635,7 +47641,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="810" spans="1:19" ht="11" customHeight="1">
+    <row r="810" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A810" s="4" t="s">
         <v>199</v>
       </c>
@@ -47685,7 +47691,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="811" spans="1:19" ht="11" customHeight="1">
+    <row r="811" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A811" s="4" t="s">
         <v>199</v>
       </c>
@@ -47735,7 +47741,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="812" spans="1:19" ht="11" customHeight="1">
+    <row r="812" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A812" s="4" t="s">
         <v>199</v>
       </c>
@@ -47792,7 +47798,7 @@
       </c>
       <c r="S812" s="6"/>
     </row>
-    <row r="813" spans="1:19" ht="11" customHeight="1">
+    <row r="813" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A813" s="4" t="s">
         <v>199</v>
       </c>
@@ -47851,7 +47857,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="814" spans="1:19" ht="11" customHeight="1">
+    <row r="814" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A814" s="4" t="s">
         <v>199</v>
       </c>
@@ -47910,7 +47916,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="815" spans="1:19" ht="11" customHeight="1">
+    <row r="815" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A815" s="4" t="s">
         <v>199</v>
       </c>
@@ -47969,7 +47975,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="816" spans="1:19" ht="11" customHeight="1">
+    <row r="816" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A816" s="4" t="s">
         <v>199</v>
       </c>
@@ -48026,7 +48032,7 @@
       </c>
       <c r="S816" s="6"/>
     </row>
-    <row r="817" spans="1:19" ht="11" customHeight="1">
+    <row r="817" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A817" s="4" t="s">
         <v>199</v>
       </c>
@@ -48085,7 +48091,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="818" spans="1:19" ht="11" customHeight="1">
+    <row r="818" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A818" s="4" t="s">
         <v>199</v>
       </c>
@@ -48144,7 +48150,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="819" spans="1:19" ht="11" customHeight="1">
+    <row r="819" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A819" s="4" t="s">
         <v>199</v>
       </c>
@@ -48203,7 +48209,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="820" spans="1:19" ht="11" customHeight="1">
+    <row r="820" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A820" s="4" t="s">
         <v>199</v>
       </c>
@@ -48260,7 +48266,7 @@
       </c>
       <c r="S820" s="6"/>
     </row>
-    <row r="821" spans="1:19" ht="11" customHeight="1">
+    <row r="821" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A821" s="4" t="s">
         <v>199</v>
       </c>
@@ -48319,7 +48325,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="822" spans="1:19" ht="11" customHeight="1">
+    <row r="822" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A822" s="4" t="s">
         <v>199</v>
       </c>
@@ -48376,7 +48382,7 @@
       </c>
       <c r="S822" s="6"/>
     </row>
-    <row r="823" spans="1:19" ht="11" customHeight="1">
+    <row r="823" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A823" s="4" t="s">
         <v>199</v>
       </c>
@@ -48433,7 +48439,7 @@
       </c>
       <c r="S823" s="6"/>
     </row>
-    <row r="824" spans="1:19" ht="11" customHeight="1">
+    <row r="824" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A824" s="4" t="s">
         <v>199</v>
       </c>
@@ -48490,7 +48496,7 @@
       </c>
       <c r="S824" s="6"/>
     </row>
-    <row r="825" spans="1:19" ht="11" customHeight="1">
+    <row r="825" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A825" s="4" t="s">
         <v>199</v>
       </c>
@@ -48547,7 +48553,7 @@
       </c>
       <c r="S825" s="6"/>
     </row>
-    <row r="826" spans="1:19" ht="11" customHeight="1">
+    <row r="826" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A826" s="4" t="s">
         <v>199</v>
       </c>
@@ -48604,7 +48610,7 @@
       </c>
       <c r="S826" s="6"/>
     </row>
-    <row r="827" spans="1:19" ht="11" customHeight="1">
+    <row r="827" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A827" s="4" t="s">
         <v>199</v>
       </c>
@@ -48661,7 +48667,7 @@
       </c>
       <c r="S827" s="6"/>
     </row>
-    <row r="828" spans="1:19" ht="11" customHeight="1">
+    <row r="828" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A828" s="4" t="s">
         <v>199</v>
       </c>
@@ -48718,7 +48724,7 @@
       </c>
       <c r="S828" s="6"/>
     </row>
-    <row r="829" spans="1:19" ht="11" customHeight="1">
+    <row r="829" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A829" s="4" t="s">
         <v>199</v>
       </c>
@@ -48775,7 +48781,7 @@
       </c>
       <c r="S829" s="6"/>
     </row>
-    <row r="830" spans="1:19" ht="11" customHeight="1">
+    <row r="830" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A830" s="4" t="s">
         <v>199</v>
       </c>
@@ -48832,7 +48838,7 @@
       </c>
       <c r="S830" s="6"/>
     </row>
-    <row r="831" spans="1:19" ht="11" customHeight="1">
+    <row r="831" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A831" s="4" t="s">
         <v>199</v>
       </c>
@@ -48889,7 +48895,7 @@
       </c>
       <c r="S831" s="6"/>
     </row>
-    <row r="832" spans="1:19" ht="11" customHeight="1">
+    <row r="832" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A832" s="4" t="s">
         <v>199</v>
       </c>
@@ -48946,7 +48952,7 @@
       </c>
       <c r="S832" s="6"/>
     </row>
-    <row r="833" spans="1:19" ht="11" customHeight="1">
+    <row r="833" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A833" s="4" t="s">
         <v>199</v>
       </c>
@@ -49005,7 +49011,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="834" spans="1:19" ht="11" customHeight="1">
+    <row r="834" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A834" s="4" t="s">
         <v>199</v>
       </c>
@@ -49062,7 +49068,7 @@
       </c>
       <c r="S834" s="6"/>
     </row>
-    <row r="835" spans="1:19" ht="11" customHeight="1">
+    <row r="835" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A835" s="4" t="s">
         <v>199</v>
       </c>
@@ -49121,7 +49127,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="836" spans="1:19" ht="11" customHeight="1">
+    <row r="836" spans="1:19" ht="11" hidden="1" customHeight="1">
       <c r="A836" s="4" t="s">
         <v>199</v>
       </c>
@@ -49179,6 +49185,13 @@
       <c r="S836" s="6"/>
     </row>
   </sheetData>
+  <autoFilter ref="C1:C836" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="448"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S836">
     <sortCondition ref="A2:A836"/>
     <sortCondition ref="B2:B836"/>
